--- a/NEW MASTER SHEET BILLING.xlsx
+++ b/NEW MASTER SHEET BILLING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Carysil_Software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E335F1-33A2-4C60-A091-C42637075CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34C565E-0F63-40F5-9FCE-8A8AEAC6CA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21486,10 +21486,10 @@
       </c>
       <c r="F24" s="109">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">

--- a/NEW MASTER SHEET BILLING.xlsx
+++ b/NEW MASTER SHEET BILLING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Carysil_Software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34C565E-0F63-40F5-9FCE-8A8AEAC6CA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A8D9BA-2CC8-4A59-B69C-3A621F022CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="767">
   <si>
     <t>Sr.No</t>
   </si>
@@ -2316,6 +2316,21 @@
   </si>
   <si>
     <t>COFFEE MAKER 01</t>
+  </si>
+  <si>
+    <t>4 BURNER</t>
+  </si>
+  <si>
+    <t>5 BURNER</t>
+  </si>
+  <si>
+    <t>1 BURNER</t>
+  </si>
+  <si>
+    <t>3 BURNER</t>
+  </si>
+  <si>
+    <t>2 BURNER</t>
   </si>
 </sst>
 </file>
@@ -21065,6 +21080,9 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
       <c r="B3" s="182" t="s">
         <v>45</v>
       </c>
@@ -21086,6 +21104,9 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="8">
+        <v>1</v>
+      </c>
       <c r="B4" s="182" t="s">
         <v>45</v>
       </c>
@@ -21107,6 +21128,9 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="8">
+        <v>1</v>
+      </c>
       <c r="B5" s="182" t="s">
         <v>45</v>
       </c>
@@ -21128,6 +21152,9 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="8">
+        <v>1</v>
+      </c>
       <c r="B6" s="182" t="s">
         <v>45</v>
       </c>
@@ -21149,6 +21176,9 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="8">
+        <v>1</v>
+      </c>
       <c r="B7" s="182" t="s">
         <v>45</v>
       </c>
@@ -21170,6 +21200,9 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="8">
+        <v>1</v>
+      </c>
       <c r="B8" s="182" t="s">
         <v>45</v>
       </c>
@@ -21191,6 +21224,9 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="8">
+        <v>1</v>
+      </c>
       <c r="B9" s="183" t="s">
         <v>45</v>
       </c>
@@ -21237,6 +21273,9 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" s="8">
+        <v>2</v>
+      </c>
       <c r="B12" s="182" t="s">
         <v>446</v>
       </c>
@@ -21258,6 +21297,9 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" s="8">
+        <v>2</v>
+      </c>
       <c r="B13" s="182" t="s">
         <v>446</v>
       </c>
@@ -21279,6 +21321,9 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="8">
+        <v>2</v>
+      </c>
       <c r="B14" s="182" t="s">
         <v>446</v>
       </c>
@@ -21300,6 +21345,9 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="8">
+        <v>2</v>
+      </c>
       <c r="B15" s="182" t="s">
         <v>446</v>
       </c>
@@ -21321,6 +21369,9 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="8">
+        <v>2</v>
+      </c>
       <c r="B16" s="182" t="s">
         <v>446</v>
       </c>
@@ -21342,6 +21393,9 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="8">
+        <v>2</v>
+      </c>
       <c r="B17" s="182" t="s">
         <v>446</v>
       </c>
@@ -21363,6 +21417,9 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="8">
+        <v>2</v>
+      </c>
       <c r="B18" s="183" t="s">
         <v>446</v>
       </c>
@@ -21409,6 +21466,9 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="8">
+        <v>3</v>
+      </c>
       <c r="B21" s="182" t="s">
         <v>543</v>
       </c>
@@ -21430,6 +21490,9 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="8">
+        <v>3</v>
+      </c>
       <c r="B22" s="182" t="s">
         <v>543</v>
       </c>
@@ -21451,6 +21514,9 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="8">
+        <v>3</v>
+      </c>
       <c r="B23" s="182" t="s">
         <v>543</v>
       </c>
@@ -21472,6 +21538,9 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="8">
+        <v>3</v>
+      </c>
       <c r="B24" s="182" t="s">
         <v>543</v>
       </c>
@@ -21493,6 +21562,9 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="8">
+        <v>3</v>
+      </c>
       <c r="B25" s="182" t="s">
         <v>543</v>
       </c>
@@ -21514,6 +21586,9 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="8">
+        <v>3</v>
+      </c>
       <c r="B26" s="182" t="s">
         <v>543</v>
       </c>
@@ -21535,6 +21610,9 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="8">
+        <v>3</v>
+      </c>
       <c r="B27" s="183" t="s">
         <v>543</v>
       </c>
@@ -21581,6 +21659,9 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="8">
+        <v>4</v>
+      </c>
       <c r="B30" s="182" t="s">
         <v>445</v>
       </c>
@@ -21602,6 +21683,9 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="8">
+        <v>4</v>
+      </c>
       <c r="B31" s="182" t="s">
         <v>445</v>
       </c>
@@ -21623,6 +21707,9 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="8">
+        <v>4</v>
+      </c>
       <c r="B32" s="182" t="s">
         <v>445</v>
       </c>
@@ -21644,6 +21731,9 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="8">
+        <v>4</v>
+      </c>
       <c r="B33" s="182" t="s">
         <v>445</v>
       </c>
@@ -21665,6 +21755,9 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="8">
+        <v>4</v>
+      </c>
       <c r="B34" s="182" t="s">
         <v>445</v>
       </c>
@@ -21686,6 +21779,9 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="8">
+        <v>4</v>
+      </c>
       <c r="B35" s="183" t="s">
         <v>445</v>
       </c>
@@ -21732,6 +21828,9 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="8">
+        <v>5</v>
+      </c>
       <c r="B38" s="182" t="s">
         <v>444</v>
       </c>
@@ -21753,6 +21852,9 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="8">
+        <v>5</v>
+      </c>
       <c r="B39" s="182" t="s">
         <v>444</v>
       </c>
@@ -21774,6 +21876,9 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="8">
+        <v>5</v>
+      </c>
       <c r="B40" s="182" t="s">
         <v>444</v>
       </c>
@@ -21795,6 +21900,9 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="8">
+        <v>5</v>
+      </c>
       <c r="B41" s="182" t="s">
         <v>444</v>
       </c>
@@ -21816,6 +21924,9 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="8">
+        <v>5</v>
+      </c>
       <c r="B42" s="182" t="s">
         <v>444</v>
       </c>
@@ -21837,6 +21948,9 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="8">
+        <v>5</v>
+      </c>
       <c r="B43" s="183" t="s">
         <v>444</v>
       </c>
@@ -21883,6 +21997,9 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="8">
+        <v>6</v>
+      </c>
       <c r="B46" s="182" t="s">
         <v>443</v>
       </c>
@@ -21904,6 +22021,9 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" s="8">
+        <v>6</v>
+      </c>
       <c r="B47" s="182" t="s">
         <v>443</v>
       </c>
@@ -21925,6 +22045,9 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="8">
+        <v>6</v>
+      </c>
       <c r="B48" s="182" t="s">
         <v>443</v>
       </c>
@@ -21946,6 +22069,9 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="8">
+        <v>6</v>
+      </c>
       <c r="B49" s="182" t="s">
         <v>443</v>
       </c>
@@ -21967,6 +22093,9 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A50" s="8">
+        <v>6</v>
+      </c>
       <c r="B50" s="182" t="s">
         <v>443</v>
       </c>
@@ -21988,6 +22117,9 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="8">
+        <v>6</v>
+      </c>
       <c r="B51" s="183" t="s">
         <v>443</v>
       </c>
@@ -22034,6 +22166,9 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" s="8">
+        <v>7</v>
+      </c>
       <c r="B54" s="182" t="s">
         <v>442</v>
       </c>
@@ -22055,6 +22190,9 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55" s="8">
+        <v>7</v>
+      </c>
       <c r="B55" s="182" t="s">
         <v>442</v>
       </c>
@@ -22076,6 +22214,9 @@
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A56" s="8">
+        <v>7</v>
+      </c>
       <c r="B56" s="182" t="s">
         <v>442</v>
       </c>
@@ -22097,6 +22238,9 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A57" s="8">
+        <v>7</v>
+      </c>
       <c r="B57" s="182" t="s">
         <v>442</v>
       </c>
@@ -22118,6 +22262,9 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A58" s="8">
+        <v>7</v>
+      </c>
       <c r="B58" s="182" t="s">
         <v>442</v>
       </c>
@@ -22139,6 +22286,9 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="8">
+        <v>7</v>
+      </c>
       <c r="B59" s="183" t="s">
         <v>442</v>
       </c>
@@ -22185,6 +22335,9 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A62" s="8">
+        <v>8</v>
+      </c>
       <c r="B62" s="185" t="s">
         <v>441</v>
       </c>
@@ -22206,6 +22359,9 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A63" s="8">
+        <v>8</v>
+      </c>
       <c r="B63" s="185" t="s">
         <v>441</v>
       </c>
@@ -22227,6 +22383,9 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A64" s="8">
+        <v>8</v>
+      </c>
       <c r="B64" s="185" t="s">
         <v>441</v>
       </c>
@@ -22248,6 +22407,9 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A65" s="8">
+        <v>8</v>
+      </c>
       <c r="B65" s="185" t="s">
         <v>441</v>
       </c>
@@ -22269,6 +22431,9 @@
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A66" s="8">
+        <v>8</v>
+      </c>
       <c r="B66" s="185" t="s">
         <v>441</v>
       </c>
@@ -22290,6 +22455,9 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="8">
+        <v>8</v>
+      </c>
       <c r="B67" s="186" t="s">
         <v>441</v>
       </c>
@@ -22341,6 +22509,9 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A70" s="8">
+        <v>9</v>
+      </c>
       <c r="B70" s="185" t="s">
         <v>440</v>
       </c>
@@ -22362,6 +22533,9 @@
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A71" s="8">
+        <v>9</v>
+      </c>
       <c r="B71" s="185" t="s">
         <v>440</v>
       </c>
@@ -22383,6 +22557,9 @@
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A72" s="8">
+        <v>9</v>
+      </c>
       <c r="B72" s="185" t="s">
         <v>440</v>
       </c>
@@ -22404,6 +22581,9 @@
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A73" s="8">
+        <v>9</v>
+      </c>
       <c r="B73" s="185" t="s">
         <v>440</v>
       </c>
@@ -22425,6 +22605,9 @@
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A74" s="8">
+        <v>9</v>
+      </c>
       <c r="B74" s="185" t="s">
         <v>440</v>
       </c>
@@ -22446,6 +22629,9 @@
       </c>
     </row>
     <row r="75" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="8">
+        <v>9</v>
+      </c>
       <c r="B75" s="186" t="s">
         <v>440</v>
       </c>
@@ -22497,6 +22683,9 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A78" s="8">
+        <v>10</v>
+      </c>
       <c r="B78" s="185" t="s">
         <v>439</v>
       </c>
@@ -22518,6 +22707,9 @@
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A79" s="8">
+        <v>10</v>
+      </c>
       <c r="B79" s="185" t="s">
         <v>439</v>
       </c>
@@ -22539,6 +22731,9 @@
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A80" s="8">
+        <v>10</v>
+      </c>
       <c r="B80" s="185" t="s">
         <v>439</v>
       </c>
@@ -22560,6 +22755,9 @@
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A81" s="8">
+        <v>10</v>
+      </c>
       <c r="B81" s="185" t="s">
         <v>439</v>
       </c>
@@ -22581,6 +22779,9 @@
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A82" s="8">
+        <v>10</v>
+      </c>
       <c r="B82" s="185" t="s">
         <v>439</v>
       </c>
@@ -22602,6 +22803,9 @@
       </c>
     </row>
     <row r="83" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="8">
+        <v>10</v>
+      </c>
       <c r="B83" s="188" t="s">
         <v>439</v>
       </c>
@@ -22653,6 +22857,9 @@
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A86" s="8">
+        <v>11</v>
+      </c>
       <c r="B86" s="185" t="s">
         <v>438</v>
       </c>
@@ -22674,6 +22881,9 @@
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A87" s="8">
+        <v>11</v>
+      </c>
       <c r="B87" s="185" t="s">
         <v>438</v>
       </c>
@@ -22695,6 +22905,9 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A88" s="8">
+        <v>11</v>
+      </c>
       <c r="B88" s="185" t="s">
         <v>438</v>
       </c>
@@ -22716,6 +22929,9 @@
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A89" s="8">
+        <v>11</v>
+      </c>
       <c r="B89" s="185" t="s">
         <v>438</v>
       </c>
@@ -22737,6 +22953,9 @@
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A90" s="8">
+        <v>11</v>
+      </c>
       <c r="B90" s="185" t="s">
         <v>438</v>
       </c>
@@ -22758,6 +22977,9 @@
       </c>
     </row>
     <row r="91" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="8">
+        <v>11</v>
+      </c>
       <c r="B91" s="186" t="s">
         <v>438</v>
       </c>
@@ -22809,6 +23031,9 @@
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A94" s="8">
+        <v>12</v>
+      </c>
       <c r="B94" s="185" t="s">
         <v>437</v>
       </c>
@@ -22830,6 +23055,9 @@
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A95" s="8">
+        <v>12</v>
+      </c>
       <c r="B95" s="185" t="s">
         <v>437</v>
       </c>
@@ -22851,6 +23079,9 @@
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A96" s="8">
+        <v>12</v>
+      </c>
       <c r="B96" s="185" t="s">
         <v>437</v>
       </c>
@@ -22872,6 +23103,9 @@
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A97" s="8">
+        <v>12</v>
+      </c>
       <c r="B97" s="185" t="s">
         <v>437</v>
       </c>
@@ -22893,6 +23127,9 @@
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A98" s="8">
+        <v>12</v>
+      </c>
       <c r="B98" s="185" t="s">
         <v>437</v>
       </c>
@@ -22914,6 +23151,9 @@
       </c>
     </row>
     <row r="99" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A99" s="8">
+        <v>12</v>
+      </c>
       <c r="B99" s="186" t="s">
         <v>437</v>
       </c>
@@ -22965,6 +23205,9 @@
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A102" s="8">
+        <v>13</v>
+      </c>
       <c r="B102" s="185" t="s">
         <v>319</v>
       </c>
@@ -22986,6 +23229,9 @@
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A103" s="8">
+        <v>13</v>
+      </c>
       <c r="B103" s="185" t="s">
         <v>319</v>
       </c>
@@ -23007,6 +23253,9 @@
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A104" s="8">
+        <v>13</v>
+      </c>
       <c r="B104" s="185" t="s">
         <v>319</v>
       </c>
@@ -23028,6 +23277,9 @@
       </c>
     </row>
     <row r="105" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A105" s="8">
+        <v>13</v>
+      </c>
       <c r="B105" s="186" t="s">
         <v>319</v>
       </c>
@@ -23079,6 +23331,9 @@
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A108" s="8">
+        <v>14</v>
+      </c>
       <c r="B108" s="185" t="s">
         <v>320</v>
       </c>
@@ -23100,6 +23355,9 @@
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A109" s="8">
+        <v>14</v>
+      </c>
       <c r="B109" s="185" t="s">
         <v>320</v>
       </c>
@@ -23121,6 +23379,9 @@
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A110" s="8">
+        <v>14</v>
+      </c>
       <c r="B110" s="185" t="s">
         <v>320</v>
       </c>
@@ -23142,6 +23403,9 @@
       </c>
     </row>
     <row r="111" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A111" s="8">
+        <v>14</v>
+      </c>
       <c r="B111" s="186" t="s">
         <v>320</v>
       </c>
@@ -23192,6 +23456,9 @@
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A114" s="8">
+        <v>15</v>
+      </c>
       <c r="B114" s="185" t="s">
         <v>321</v>
       </c>
@@ -23213,6 +23480,9 @@
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A115" s="8">
+        <v>15</v>
+      </c>
       <c r="B115" s="185" t="s">
         <v>321</v>
       </c>
@@ -23234,6 +23504,9 @@
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A116" s="8">
+        <v>15</v>
+      </c>
       <c r="B116" s="185" t="s">
         <v>321</v>
       </c>
@@ -23255,6 +23528,9 @@
       </c>
     </row>
     <row r="117" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A117" s="8">
+        <v>15</v>
+      </c>
       <c r="B117" s="186" t="s">
         <v>321</v>
       </c>
@@ -23304,6 +23580,9 @@
       <c r="G119" s="104"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A120" s="8">
+        <v>16</v>
+      </c>
       <c r="B120" s="185" t="s">
         <v>436</v>
       </c>
@@ -23323,6 +23602,9 @@
       <c r="G120" s="105"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A121" s="8">
+        <v>16</v>
+      </c>
       <c r="B121" s="185" t="s">
         <v>436</v>
       </c>
@@ -23342,6 +23624,9 @@
       <c r="G121" s="105"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A122" s="8">
+        <v>16</v>
+      </c>
       <c r="B122" s="185" t="s">
         <v>436</v>
       </c>
@@ -23361,6 +23646,9 @@
       <c r="G122" s="105"/>
     </row>
     <row r="123" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A123" s="8">
+        <v>16</v>
+      </c>
       <c r="B123" s="186" t="s">
         <v>436</v>
       </c>
@@ -23408,6 +23696,9 @@
       <c r="G125" s="104"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A126" s="8">
+        <v>17</v>
+      </c>
       <c r="B126" s="185" t="s">
         <v>435</v>
       </c>
@@ -23427,6 +23718,9 @@
       <c r="G126" s="105"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A127" s="8">
+        <v>17</v>
+      </c>
       <c r="B127" s="185" t="s">
         <v>435</v>
       </c>
@@ -23446,6 +23740,9 @@
       <c r="G127" s="105"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A128" s="8">
+        <v>17</v>
+      </c>
       <c r="B128" s="185" t="s">
         <v>435</v>
       </c>
@@ -23465,6 +23762,9 @@
       <c r="G128" s="105"/>
     </row>
     <row r="129" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A129" s="8">
+        <v>17</v>
+      </c>
       <c r="B129" s="186" t="s">
         <v>435</v>
       </c>
@@ -23512,6 +23812,9 @@
       <c r="G131" s="104"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A132" s="8">
+        <v>18</v>
+      </c>
       <c r="B132" s="185" t="s">
         <v>434</v>
       </c>
@@ -23531,6 +23834,9 @@
       <c r="G132" s="105"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A133" s="8">
+        <v>18</v>
+      </c>
       <c r="B133" s="185" t="s">
         <v>434</v>
       </c>
@@ -23550,6 +23856,9 @@
       <c r="G133" s="105"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A134" s="8">
+        <v>18</v>
+      </c>
       <c r="B134" s="185" t="s">
         <v>434</v>
       </c>
@@ -23569,6 +23878,9 @@
       <c r="G134" s="105"/>
     </row>
     <row r="135" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A135" s="8">
+        <v>18</v>
+      </c>
       <c r="B135" s="186" t="s">
         <v>434</v>
       </c>
@@ -23618,6 +23930,9 @@
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A138" s="8">
+        <v>19</v>
+      </c>
       <c r="B138" s="185" t="s">
         <v>286</v>
       </c>
@@ -23639,6 +23954,9 @@
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A139" s="8">
+        <v>19</v>
+      </c>
       <c r="B139" s="185" t="s">
         <v>286</v>
       </c>
@@ -23660,6 +23978,9 @@
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A140" s="8">
+        <v>19</v>
+      </c>
       <c r="B140" s="185" t="s">
         <v>286</v>
       </c>
@@ -23681,6 +24002,9 @@
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A141" s="8">
+        <v>19</v>
+      </c>
       <c r="B141" s="185" t="s">
         <v>286</v>
       </c>
@@ -23702,6 +24026,9 @@
       </c>
     </row>
     <row r="142" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A142" s="8">
+        <v>19</v>
+      </c>
       <c r="B142" s="183" t="s">
         <v>286</v>
       </c>
@@ -23748,6 +24075,9 @@
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A145" s="8">
+        <v>20</v>
+      </c>
       <c r="B145" s="185" t="s">
         <v>287</v>
       </c>
@@ -23769,6 +24099,9 @@
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A146" s="8">
+        <v>20</v>
+      </c>
       <c r="B146" s="185" t="s">
         <v>287</v>
       </c>
@@ -23790,6 +24123,9 @@
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A147" s="8">
+        <v>20</v>
+      </c>
       <c r="B147" s="185" t="s">
         <v>287</v>
       </c>
@@ -23811,6 +24147,9 @@
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A148" s="8">
+        <v>20</v>
+      </c>
       <c r="B148" s="185" t="s">
         <v>287</v>
       </c>
@@ -23832,6 +24171,9 @@
       </c>
     </row>
     <row r="149" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A149" s="8">
+        <v>20</v>
+      </c>
       <c r="B149" s="183" t="s">
         <v>287</v>
       </c>
@@ -23878,6 +24220,9 @@
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A152" s="8">
+        <v>21</v>
+      </c>
       <c r="B152" s="182" t="s">
         <v>433</v>
       </c>
@@ -23899,6 +24244,9 @@
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A153" s="8">
+        <v>21</v>
+      </c>
       <c r="B153" s="182" t="s">
         <v>433</v>
       </c>
@@ -23920,6 +24268,9 @@
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A154" s="8">
+        <v>21</v>
+      </c>
       <c r="B154" s="182" t="s">
         <v>433</v>
       </c>
@@ -23941,6 +24292,9 @@
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A155" s="8">
+        <v>21</v>
+      </c>
       <c r="B155" s="182" t="s">
         <v>433</v>
       </c>
@@ -23962,6 +24316,9 @@
       </c>
     </row>
     <row r="156" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A156" s="8">
+        <v>21</v>
+      </c>
       <c r="B156" s="183" t="s">
         <v>433</v>
       </c>
@@ -24008,6 +24365,9 @@
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A159" s="8">
+        <v>22</v>
+      </c>
       <c r="B159" s="182" t="s">
         <v>432</v>
       </c>
@@ -24029,6 +24389,9 @@
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A160" s="8">
+        <v>22</v>
+      </c>
       <c r="B160" s="182" t="s">
         <v>432</v>
       </c>
@@ -24050,6 +24413,9 @@
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A161" s="8">
+        <v>22</v>
+      </c>
       <c r="B161" s="182" t="s">
         <v>432</v>
       </c>
@@ -24071,6 +24437,9 @@
       </c>
     </row>
     <row r="162" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A162" s="8">
+        <v>22</v>
+      </c>
       <c r="B162" s="183" t="s">
         <v>432</v>
       </c>
@@ -24117,6 +24486,9 @@
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A165" s="8">
+        <v>23</v>
+      </c>
       <c r="B165" s="182" t="s">
         <v>431</v>
       </c>
@@ -24138,6 +24510,9 @@
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A166" s="8">
+        <v>23</v>
+      </c>
       <c r="B166" s="182" t="s">
         <v>431</v>
       </c>
@@ -24159,6 +24534,9 @@
       </c>
     </row>
     <row r="167" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A167" s="8">
+        <v>23</v>
+      </c>
       <c r="B167" s="183" t="s">
         <v>431</v>
       </c>
@@ -24205,6 +24583,9 @@
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A170" s="8">
+        <v>24</v>
+      </c>
       <c r="B170" s="182" t="s">
         <v>430</v>
       </c>
@@ -24226,6 +24607,9 @@
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A171" s="8">
+        <v>24</v>
+      </c>
       <c r="B171" s="182" t="s">
         <v>430</v>
       </c>
@@ -24247,6 +24631,9 @@
       </c>
     </row>
     <row r="172" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A172" s="8">
+        <v>24</v>
+      </c>
       <c r="B172" s="183" t="s">
         <v>430</v>
       </c>
@@ -24368,6 +24755,9 @@
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A181" s="8">
+        <v>28</v>
+      </c>
       <c r="B181" s="182" t="s">
         <v>288</v>
       </c>
@@ -24389,6 +24779,9 @@
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A182" s="8">
+        <v>28</v>
+      </c>
       <c r="B182" s="182" t="s">
         <v>288</v>
       </c>
@@ -24410,6 +24803,9 @@
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A183" s="8">
+        <v>28</v>
+      </c>
       <c r="B183" s="182" t="s">
         <v>288</v>
       </c>
@@ -24431,6 +24827,9 @@
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A184" s="8">
+        <v>28</v>
+      </c>
       <c r="B184" s="182" t="s">
         <v>288</v>
       </c>
@@ -24452,6 +24851,9 @@
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A185" s="8">
+        <v>28</v>
+      </c>
       <c r="B185" s="182" t="s">
         <v>288</v>
       </c>
@@ -24473,6 +24875,9 @@
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A186" s="8">
+        <v>28</v>
+      </c>
       <c r="B186" s="182" t="s">
         <v>288</v>
       </c>
@@ -24494,6 +24899,9 @@
       </c>
     </row>
     <row r="187" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A187" s="8">
+        <v>28</v>
+      </c>
       <c r="B187" s="183" t="s">
         <v>288</v>
       </c>
@@ -24540,6 +24948,9 @@
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A190" s="8">
+        <v>29</v>
+      </c>
       <c r="B190" s="182" t="s">
         <v>289</v>
       </c>
@@ -24561,6 +24972,9 @@
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A191" s="8">
+        <v>29</v>
+      </c>
       <c r="B191" s="182" t="s">
         <v>289</v>
       </c>
@@ -24582,6 +24996,9 @@
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A192" s="8">
+        <v>29</v>
+      </c>
       <c r="B192" s="182" t="s">
         <v>289</v>
       </c>
@@ -24603,6 +25020,9 @@
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A193" s="8">
+        <v>29</v>
+      </c>
       <c r="B193" s="182" t="s">
         <v>289</v>
       </c>
@@ -24624,6 +25044,9 @@
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A194" s="8">
+        <v>29</v>
+      </c>
       <c r="B194" s="182" t="s">
         <v>289</v>
       </c>
@@ -24645,6 +25068,9 @@
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A195" s="8">
+        <v>29</v>
+      </c>
       <c r="B195" s="182" t="s">
         <v>289</v>
       </c>
@@ -24666,6 +25092,9 @@
       </c>
     </row>
     <row r="196" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A196" s="8">
+        <v>29</v>
+      </c>
       <c r="B196" s="183" t="s">
         <v>289</v>
       </c>
@@ -24712,6 +25141,9 @@
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A199" s="8">
+        <v>30</v>
+      </c>
       <c r="B199" s="182" t="s">
         <v>615</v>
       </c>
@@ -24733,6 +25165,9 @@
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A200" s="8">
+        <v>30</v>
+      </c>
       <c r="B200" s="182" t="s">
         <v>615</v>
       </c>
@@ -24754,6 +25189,9 @@
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A201" s="8">
+        <v>30</v>
+      </c>
       <c r="B201" s="182" t="s">
         <v>615</v>
       </c>
@@ -24775,6 +25213,9 @@
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A202" s="8">
+        <v>30</v>
+      </c>
       <c r="B202" s="182" t="s">
         <v>615</v>
       </c>
@@ -24796,6 +25237,9 @@
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A203" s="8">
+        <v>30</v>
+      </c>
       <c r="B203" s="182" t="s">
         <v>615</v>
       </c>
@@ -24817,6 +25261,9 @@
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A204" s="8">
+        <v>30</v>
+      </c>
       <c r="B204" s="182" t="s">
         <v>615</v>
       </c>
@@ -24838,6 +25285,9 @@
       </c>
     </row>
     <row r="205" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A205" s="8">
+        <v>30</v>
+      </c>
       <c r="B205" s="183" t="s">
         <v>615</v>
       </c>
@@ -24884,6 +25334,9 @@
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A208" s="8">
+        <v>31</v>
+      </c>
       <c r="B208" s="182" t="s">
         <v>614</v>
       </c>
@@ -24905,6 +25358,9 @@
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A209" s="8">
+        <v>31</v>
+      </c>
       <c r="B209" s="182" t="s">
         <v>614</v>
       </c>
@@ -24926,6 +25382,9 @@
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A210" s="8">
+        <v>31</v>
+      </c>
       <c r="B210" s="182" t="s">
         <v>614</v>
       </c>
@@ -24947,6 +25406,9 @@
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A211" s="8">
+        <v>31</v>
+      </c>
       <c r="B211" s="182" t="s">
         <v>614</v>
       </c>
@@ -24968,6 +25430,9 @@
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A212" s="8">
+        <v>31</v>
+      </c>
       <c r="B212" s="182" t="s">
         <v>614</v>
       </c>
@@ -24989,6 +25454,9 @@
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A213" s="8">
+        <v>31</v>
+      </c>
       <c r="B213" s="182" t="s">
         <v>614</v>
       </c>
@@ -25010,6 +25478,9 @@
       </c>
     </row>
     <row r="214" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A214" s="8">
+        <v>31</v>
+      </c>
       <c r="B214" s="183" t="s">
         <v>614</v>
       </c>
@@ -25056,6 +25527,9 @@
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A217" s="8">
+        <v>32</v>
+      </c>
       <c r="B217" s="182" t="s">
         <v>292</v>
       </c>
@@ -25077,6 +25551,9 @@
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A218" s="8">
+        <v>32</v>
+      </c>
       <c r="B218" s="182" t="s">
         <v>292</v>
       </c>
@@ -25098,6 +25575,9 @@
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A219" s="8">
+        <v>32</v>
+      </c>
       <c r="B219" s="182" t="s">
         <v>292</v>
       </c>
@@ -25119,6 +25599,9 @@
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A220" s="8">
+        <v>32</v>
+      </c>
       <c r="B220" s="182" t="s">
         <v>292</v>
       </c>
@@ -25140,6 +25623,9 @@
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A221" s="8">
+        <v>32</v>
+      </c>
       <c r="B221" s="182" t="s">
         <v>292</v>
       </c>
@@ -25161,6 +25647,9 @@
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A222" s="8">
+        <v>32</v>
+      </c>
       <c r="B222" s="182" t="s">
         <v>292</v>
       </c>
@@ -25182,6 +25671,9 @@
       </c>
     </row>
     <row r="223" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A223" s="8">
+        <v>32</v>
+      </c>
       <c r="B223" s="183" t="s">
         <v>292</v>
       </c>
@@ -25228,6 +25720,9 @@
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A226" s="8">
+        <v>33</v>
+      </c>
       <c r="B226" s="182" t="s">
         <v>575</v>
       </c>
@@ -25249,6 +25744,9 @@
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A227" s="8">
+        <v>33</v>
+      </c>
       <c r="B227" s="182" t="s">
         <v>575</v>
       </c>
@@ -25270,6 +25768,9 @@
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A228" s="8">
+        <v>33</v>
+      </c>
       <c r="B228" s="182" t="s">
         <v>575</v>
       </c>
@@ -25291,6 +25792,9 @@
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A229" s="8">
+        <v>33</v>
+      </c>
       <c r="B229" s="182" t="s">
         <v>575</v>
       </c>
@@ -25312,6 +25816,9 @@
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A230" s="8">
+        <v>33</v>
+      </c>
       <c r="B230" s="182" t="s">
         <v>575</v>
       </c>
@@ -25333,6 +25840,9 @@
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A231" s="8">
+        <v>33</v>
+      </c>
       <c r="B231" s="182" t="s">
         <v>575</v>
       </c>
@@ -25354,6 +25864,9 @@
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A232" s="8">
+        <v>33</v>
+      </c>
       <c r="B232" s="182" t="s">
         <v>575</v>
       </c>
@@ -25375,6 +25888,9 @@
       </c>
     </row>
     <row r="233" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A233" s="8">
+        <v>33</v>
+      </c>
       <c r="B233" s="183" t="s">
         <v>575</v>
       </c>
@@ -25421,6 +25937,9 @@
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A236" s="8">
+        <v>34</v>
+      </c>
       <c r="B236" s="182" t="s">
         <v>574</v>
       </c>
@@ -25442,6 +25961,9 @@
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A237" s="8">
+        <v>34</v>
+      </c>
       <c r="B237" s="182" t="s">
         <v>574</v>
       </c>
@@ -25463,6 +25985,9 @@
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A238" s="8">
+        <v>34</v>
+      </c>
       <c r="B238" s="182" t="s">
         <v>574</v>
       </c>
@@ -25484,6 +26009,9 @@
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A239" s="8">
+        <v>34</v>
+      </c>
       <c r="B239" s="182" t="s">
         <v>574</v>
       </c>
@@ -25505,6 +26033,9 @@
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A240" s="8">
+        <v>34</v>
+      </c>
       <c r="B240" s="182" t="s">
         <v>574</v>
       </c>
@@ -25526,6 +26057,9 @@
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A241" s="8">
+        <v>34</v>
+      </c>
       <c r="B241" s="182" t="s">
         <v>574</v>
       </c>
@@ -25547,6 +26081,9 @@
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A242" s="8">
+        <v>34</v>
+      </c>
       <c r="B242" s="182" t="s">
         <v>574</v>
       </c>
@@ -25568,6 +26105,9 @@
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A243" s="8">
+        <v>34</v>
+      </c>
       <c r="B243" s="182" t="s">
         <v>574</v>
       </c>
@@ -25589,6 +26129,9 @@
       </c>
     </row>
     <row r="244" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A244" s="8">
+        <v>34</v>
+      </c>
       <c r="B244" s="183" t="s">
         <v>574</v>
       </c>
@@ -25637,6 +26180,9 @@
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A247" s="8">
+        <v>35</v>
+      </c>
       <c r="B247" s="182" t="s">
         <v>576</v>
       </c>
@@ -25658,6 +26204,9 @@
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A248" s="8">
+        <v>35</v>
+      </c>
       <c r="B248" s="182" t="s">
         <v>576</v>
       </c>
@@ -25679,6 +26228,9 @@
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A249" s="8">
+        <v>35</v>
+      </c>
       <c r="B249" s="182" t="s">
         <v>576</v>
       </c>
@@ -25700,6 +26252,9 @@
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A250" s="8">
+        <v>35</v>
+      </c>
       <c r="B250" s="182" t="s">
         <v>576</v>
       </c>
@@ -25721,6 +26276,9 @@
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A251" s="8">
+        <v>35</v>
+      </c>
       <c r="B251" s="182" t="s">
         <v>576</v>
       </c>
@@ -25742,6 +26300,9 @@
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A252" s="8">
+        <v>35</v>
+      </c>
       <c r="B252" s="182" t="s">
         <v>576</v>
       </c>
@@ -25763,6 +26324,9 @@
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A253" s="8">
+        <v>35</v>
+      </c>
       <c r="B253" s="182" t="s">
         <v>576</v>
       </c>
@@ -25784,6 +26348,9 @@
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A254" s="8">
+        <v>35</v>
+      </c>
       <c r="B254" s="182" t="s">
         <v>576</v>
       </c>
@@ -25805,6 +26372,9 @@
       </c>
     </row>
     <row r="255" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A255" s="8">
+        <v>35</v>
+      </c>
       <c r="B255" s="183" t="s">
         <v>576</v>
       </c>
@@ -25851,6 +26421,9 @@
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A258" s="8">
+        <v>36</v>
+      </c>
       <c r="B258" s="182" t="s">
         <v>428</v>
       </c>
@@ -25872,6 +26445,9 @@
       </c>
     </row>
     <row r="259" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A259" s="8">
+        <v>36</v>
+      </c>
       <c r="B259" s="182" t="s">
         <v>428</v>
       </c>
@@ -25893,6 +26469,9 @@
       </c>
     </row>
     <row r="260" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A260" s="8">
+        <v>36</v>
+      </c>
       <c r="B260" s="183" t="s">
         <v>428</v>
       </c>
@@ -25938,6 +26517,9 @@
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A263" s="8">
+        <v>37</v>
+      </c>
       <c r="B263" s="182" t="s">
         <v>427</v>
       </c>
@@ -25959,6 +26541,9 @@
       </c>
     </row>
     <row r="264" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A264" s="8">
+        <v>37</v>
+      </c>
       <c r="B264" s="183" t="s">
         <v>427</v>
       </c>
@@ -26005,6 +26590,9 @@
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A267" s="8">
+        <v>38</v>
+      </c>
       <c r="B267" s="182" t="s">
         <v>538</v>
       </c>
@@ -26026,6 +26614,9 @@
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A268" s="8">
+        <v>38</v>
+      </c>
       <c r="B268" s="182" t="s">
         <v>538</v>
       </c>
@@ -26047,6 +26638,9 @@
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A269" s="8">
+        <v>38</v>
+      </c>
       <c r="B269" s="182" t="s">
         <v>538</v>
       </c>
@@ -26068,6 +26662,9 @@
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A270" s="8">
+        <v>38</v>
+      </c>
       <c r="B270" s="182" t="s">
         <v>538</v>
       </c>
@@ -26089,6 +26686,9 @@
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A271" s="8">
+        <v>38</v>
+      </c>
       <c r="B271" s="182" t="s">
         <v>538</v>
       </c>
@@ -26110,6 +26710,9 @@
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A272" s="8">
+        <v>38</v>
+      </c>
       <c r="B272" s="182" t="s">
         <v>538</v>
       </c>
@@ -26131,6 +26734,9 @@
       </c>
     </row>
     <row r="273" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A273" s="8">
+        <v>38</v>
+      </c>
       <c r="B273" s="183" t="s">
         <v>538</v>
       </c>
@@ -26202,6 +26808,9 @@
       </c>
     </row>
     <row r="278" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A278" s="8">
+        <v>40</v>
+      </c>
       <c r="B278" s="183" t="s">
         <v>426</v>
       </c>
@@ -26248,6 +26857,9 @@
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A281" s="8">
+        <v>41</v>
+      </c>
       <c r="B281" s="182" t="s">
         <v>425</v>
       </c>
@@ -26269,6 +26881,9 @@
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A282" s="8">
+        <v>41</v>
+      </c>
       <c r="B282" s="182" t="s">
         <v>425</v>
       </c>
@@ -26290,6 +26905,9 @@
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A283" s="8">
+        <v>41</v>
+      </c>
       <c r="B283" s="182" t="s">
         <v>425</v>
       </c>
@@ -26311,6 +26929,9 @@
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A284" s="8">
+        <v>41</v>
+      </c>
       <c r="B284" s="182" t="s">
         <v>425</v>
       </c>
@@ -26332,6 +26953,9 @@
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A285" s="8">
+        <v>41</v>
+      </c>
       <c r="B285" s="182" t="s">
         <v>425</v>
       </c>
@@ -26353,6 +26977,9 @@
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A286" s="8">
+        <v>41</v>
+      </c>
       <c r="B286" s="182" t="s">
         <v>425</v>
       </c>
@@ -26374,6 +27001,9 @@
       </c>
     </row>
     <row r="287" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A287" s="8">
+        <v>41</v>
+      </c>
       <c r="B287" s="183" t="s">
         <v>425</v>
       </c>
@@ -26420,6 +27050,9 @@
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A290" s="8">
+        <v>42</v>
+      </c>
       <c r="B290" s="182" t="s">
         <v>424</v>
       </c>
@@ -26441,6 +27074,9 @@
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A291" s="8">
+        <v>42</v>
+      </c>
       <c r="B291" s="182" t="s">
         <v>424</v>
       </c>
@@ -26462,6 +27098,9 @@
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A292" s="8">
+        <v>42</v>
+      </c>
       <c r="B292" s="182" t="s">
         <v>424</v>
       </c>
@@ -26483,6 +27122,9 @@
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A293" s="8">
+        <v>42</v>
+      </c>
       <c r="B293" s="182" t="s">
         <v>424</v>
       </c>
@@ -26504,6 +27146,9 @@
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A294" s="8">
+        <v>42</v>
+      </c>
       <c r="B294" s="182" t="s">
         <v>424</v>
       </c>
@@ -26525,6 +27170,9 @@
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A295" s="8">
+        <v>42</v>
+      </c>
       <c r="B295" s="182" t="s">
         <v>424</v>
       </c>
@@ -26546,6 +27194,9 @@
       </c>
     </row>
     <row r="296" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A296" s="8">
+        <v>42</v>
+      </c>
       <c r="B296" s="183" t="s">
         <v>424</v>
       </c>
@@ -26592,6 +27243,9 @@
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A299" s="8">
+        <v>43</v>
+      </c>
       <c r="B299" s="182" t="s">
         <v>423</v>
       </c>
@@ -26613,6 +27267,9 @@
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A300" s="8">
+        <v>43</v>
+      </c>
       <c r="B300" s="182" t="s">
         <v>423</v>
       </c>
@@ -26634,6 +27291,9 @@
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A301" s="8">
+        <v>43</v>
+      </c>
       <c r="B301" s="182" t="s">
         <v>423</v>
       </c>
@@ -26655,6 +27315,9 @@
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A302" s="8">
+        <v>43</v>
+      </c>
       <c r="B302" s="182" t="s">
         <v>423</v>
       </c>
@@ -26676,6 +27339,9 @@
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A303" s="8">
+        <v>43</v>
+      </c>
       <c r="B303" s="182" t="s">
         <v>423</v>
       </c>
@@ -26697,6 +27363,9 @@
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A304" s="8">
+        <v>43</v>
+      </c>
       <c r="B304" s="182" t="s">
         <v>423</v>
       </c>
@@ -26718,6 +27387,9 @@
       </c>
     </row>
     <row r="305" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A305" s="8">
+        <v>43</v>
+      </c>
       <c r="B305" s="183" t="s">
         <v>423</v>
       </c>
@@ -26764,6 +27436,9 @@
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A308" s="8">
+        <v>44</v>
+      </c>
       <c r="B308" s="182" t="s">
         <v>422</v>
       </c>
@@ -26785,6 +27460,9 @@
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A309" s="8">
+        <v>44</v>
+      </c>
       <c r="B309" s="182" t="s">
         <v>422</v>
       </c>
@@ -26806,6 +27484,9 @@
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A310" s="8">
+        <v>44</v>
+      </c>
       <c r="B310" s="182" t="s">
         <v>422</v>
       </c>
@@ -26827,6 +27508,9 @@
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A311" s="8">
+        <v>44</v>
+      </c>
       <c r="B311" s="182" t="s">
         <v>422</v>
       </c>
@@ -26848,6 +27532,9 @@
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A312" s="8">
+        <v>44</v>
+      </c>
       <c r="B312" s="182" t="s">
         <v>422</v>
       </c>
@@ -26869,6 +27556,9 @@
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A313" s="8">
+        <v>44</v>
+      </c>
       <c r="B313" s="182" t="s">
         <v>422</v>
       </c>
@@ -26890,6 +27580,9 @@
       </c>
     </row>
     <row r="314" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A314" s="8">
+        <v>44</v>
+      </c>
       <c r="B314" s="183" t="s">
         <v>422</v>
       </c>
@@ -26936,6 +27629,9 @@
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A317" s="8">
+        <v>45</v>
+      </c>
       <c r="B317" s="182" t="s">
         <v>40</v>
       </c>
@@ -26957,6 +27653,9 @@
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A318" s="8">
+        <v>45</v>
+      </c>
       <c r="B318" s="182" t="s">
         <v>40</v>
       </c>
@@ -26978,6 +27677,9 @@
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A319" s="8">
+        <v>45</v>
+      </c>
       <c r="B319" s="182" t="s">
         <v>40</v>
       </c>
@@ -26999,6 +27701,9 @@
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A320" s="8">
+        <v>45</v>
+      </c>
       <c r="B320" s="182" t="s">
         <v>40</v>
       </c>
@@ -27020,6 +27725,9 @@
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A321" s="8">
+        <v>45</v>
+      </c>
       <c r="B321" s="182" t="s">
         <v>40</v>
       </c>
@@ -27041,6 +27749,9 @@
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A322" s="8">
+        <v>45</v>
+      </c>
       <c r="B322" s="182" t="s">
         <v>40</v>
       </c>
@@ -27062,6 +27773,9 @@
       </c>
     </row>
     <row r="323" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A323" s="8">
+        <v>45</v>
+      </c>
       <c r="B323" s="183" t="s">
         <v>40</v>
       </c>
@@ -27108,6 +27822,9 @@
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A326" s="8">
+        <v>46</v>
+      </c>
       <c r="B326" s="182" t="s">
         <v>41</v>
       </c>
@@ -27129,6 +27846,9 @@
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A327" s="8">
+        <v>46</v>
+      </c>
       <c r="B327" s="182" t="s">
         <v>41</v>
       </c>
@@ -27150,6 +27870,9 @@
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A328" s="8">
+        <v>46</v>
+      </c>
       <c r="B328" s="182" t="s">
         <v>41</v>
       </c>
@@ -27171,6 +27894,9 @@
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A329" s="8">
+        <v>46</v>
+      </c>
       <c r="B329" s="182" t="s">
         <v>41</v>
       </c>
@@ -27192,6 +27918,9 @@
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A330" s="8">
+        <v>46</v>
+      </c>
       <c r="B330" s="182" t="s">
         <v>41</v>
       </c>
@@ -27213,6 +27942,9 @@
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A331" s="8">
+        <v>46</v>
+      </c>
       <c r="B331" s="182" t="s">
         <v>41</v>
       </c>
@@ -27234,6 +27966,9 @@
       </c>
     </row>
     <row r="332" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A332" s="8">
+        <v>46</v>
+      </c>
       <c r="B332" s="183" t="s">
         <v>41</v>
       </c>
@@ -27284,6 +28019,9 @@
       </c>
     </row>
     <row r="335" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A335" s="8">
+        <v>47</v>
+      </c>
       <c r="B335" s="182" t="s">
         <v>421</v>
       </c>
@@ -27305,6 +28043,9 @@
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A336" s="8">
+        <v>47</v>
+      </c>
       <c r="B336" s="182" t="s">
         <v>421</v>
       </c>
@@ -27326,6 +28067,9 @@
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A337" s="8">
+        <v>47</v>
+      </c>
       <c r="B337" s="182" t="s">
         <v>421</v>
       </c>
@@ -27347,6 +28091,9 @@
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A338" s="8">
+        <v>47</v>
+      </c>
       <c r="B338" s="182" t="s">
         <v>421</v>
       </c>
@@ -27368,6 +28115,9 @@
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A339" s="8">
+        <v>47</v>
+      </c>
       <c r="B339" s="182" t="s">
         <v>421</v>
       </c>
@@ -27389,6 +28139,9 @@
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A340" s="8">
+        <v>47</v>
+      </c>
       <c r="B340" s="182" t="s">
         <v>421</v>
       </c>
@@ -27410,6 +28163,9 @@
       </c>
     </row>
     <row r="341" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A341" s="8">
+        <v>47</v>
+      </c>
       <c r="B341" s="183" t="s">
         <v>421</v>
       </c>
@@ -27456,6 +28212,9 @@
       </c>
     </row>
     <row r="344" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A344" s="8">
+        <v>48</v>
+      </c>
       <c r="B344" s="182" t="s">
         <v>420</v>
       </c>
@@ -27477,6 +28236,9 @@
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A345" s="8">
+        <v>48</v>
+      </c>
       <c r="B345" s="182" t="s">
         <v>420</v>
       </c>
@@ -27498,6 +28260,9 @@
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A346" s="8">
+        <v>48</v>
+      </c>
       <c r="B346" s="182" t="s">
         <v>420</v>
       </c>
@@ -27519,6 +28284,9 @@
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A347" s="8">
+        <v>48</v>
+      </c>
       <c r="B347" s="182" t="s">
         <v>420</v>
       </c>
@@ -27540,6 +28308,9 @@
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A348" s="8">
+        <v>48</v>
+      </c>
       <c r="B348" s="182" t="s">
         <v>420</v>
       </c>
@@ -27561,6 +28332,9 @@
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A349" s="8">
+        <v>48</v>
+      </c>
       <c r="B349" s="182" t="s">
         <v>420</v>
       </c>
@@ -27582,6 +28356,9 @@
       </c>
     </row>
     <row r="350" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A350" s="8">
+        <v>48</v>
+      </c>
       <c r="B350" s="183" t="s">
         <v>420</v>
       </c>
@@ -27628,6 +28405,9 @@
       </c>
     </row>
     <row r="353" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A353" s="8">
+        <v>49</v>
+      </c>
       <c r="B353" s="182" t="s">
         <v>419</v>
       </c>
@@ -27649,6 +28429,9 @@
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A354" s="8">
+        <v>49</v>
+      </c>
       <c r="B354" s="182" t="s">
         <v>419</v>
       </c>
@@ -27670,6 +28453,9 @@
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A355" s="8">
+        <v>49</v>
+      </c>
       <c r="B355" s="182" t="s">
         <v>419</v>
       </c>
@@ -27691,6 +28477,9 @@
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A356" s="8">
+        <v>49</v>
+      </c>
       <c r="B356" s="182" t="s">
         <v>419</v>
       </c>
@@ -27712,6 +28501,9 @@
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A357" s="8">
+        <v>49</v>
+      </c>
       <c r="B357" s="182" t="s">
         <v>419</v>
       </c>
@@ -27733,6 +28525,9 @@
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A358" s="8">
+        <v>49</v>
+      </c>
       <c r="B358" s="182" t="s">
         <v>419</v>
       </c>
@@ -27754,6 +28549,9 @@
       </c>
     </row>
     <row r="359" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A359" s="8">
+        <v>49</v>
+      </c>
       <c r="B359" s="183" t="s">
         <v>419</v>
       </c>
@@ -27800,6 +28598,9 @@
       </c>
     </row>
     <row r="362" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A362" s="8">
+        <v>50</v>
+      </c>
       <c r="B362" s="182" t="s">
         <v>418</v>
       </c>
@@ -27821,6 +28622,9 @@
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A363" s="8">
+        <v>50</v>
+      </c>
       <c r="B363" s="182" t="s">
         <v>418</v>
       </c>
@@ -27842,6 +28646,9 @@
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A364" s="8">
+        <v>50</v>
+      </c>
       <c r="B364" s="182" t="s">
         <v>418</v>
       </c>
@@ -27863,6 +28670,9 @@
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A365" s="8">
+        <v>50</v>
+      </c>
       <c r="B365" s="182" t="s">
         <v>418</v>
       </c>
@@ -27884,6 +28694,9 @@
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A366" s="8">
+        <v>50</v>
+      </c>
       <c r="B366" s="182" t="s">
         <v>418</v>
       </c>
@@ -27905,6 +28718,9 @@
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A367" s="8">
+        <v>50</v>
+      </c>
       <c r="B367" s="182" t="s">
         <v>418</v>
       </c>
@@ -27926,6 +28742,9 @@
       </c>
     </row>
     <row r="368" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A368" s="8">
+        <v>50</v>
+      </c>
       <c r="B368" s="183" t="s">
         <v>418</v>
       </c>
@@ -27972,6 +28791,9 @@
       </c>
     </row>
     <row r="371" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A371" s="8">
+        <v>51</v>
+      </c>
       <c r="B371" s="182" t="s">
         <v>417</v>
       </c>
@@ -27993,6 +28815,9 @@
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A372" s="8">
+        <v>51</v>
+      </c>
       <c r="B372" s="182" t="s">
         <v>417</v>
       </c>
@@ -28014,6 +28839,9 @@
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A373" s="8">
+        <v>51</v>
+      </c>
       <c r="B373" s="182" t="s">
         <v>417</v>
       </c>
@@ -28035,6 +28863,9 @@
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A374" s="8">
+        <v>51</v>
+      </c>
       <c r="B374" s="182" t="s">
         <v>417</v>
       </c>
@@ -28056,6 +28887,9 @@
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A375" s="8">
+        <v>51</v>
+      </c>
       <c r="B375" s="182" t="s">
         <v>417</v>
       </c>
@@ -28077,6 +28911,9 @@
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A376" s="8">
+        <v>51</v>
+      </c>
       <c r="B376" s="182" t="s">
         <v>417</v>
       </c>
@@ -28098,6 +28935,9 @@
       </c>
     </row>
     <row r="377" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A377" s="8">
+        <v>51</v>
+      </c>
       <c r="B377" s="183" t="s">
         <v>417</v>
       </c>
@@ -28144,6 +28984,9 @@
       </c>
     </row>
     <row r="380" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A380" s="8">
+        <v>52</v>
+      </c>
       <c r="B380" s="182" t="s">
         <v>596</v>
       </c>
@@ -28165,6 +29008,9 @@
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A381" s="8">
+        <v>52</v>
+      </c>
       <c r="B381" s="182" t="s">
         <v>596</v>
       </c>
@@ -28186,6 +29032,9 @@
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A382" s="8">
+        <v>52</v>
+      </c>
       <c r="B382" s="182" t="s">
         <v>596</v>
       </c>
@@ -28207,6 +29056,9 @@
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A383" s="8">
+        <v>52</v>
+      </c>
       <c r="B383" s="182" t="s">
         <v>596</v>
       </c>
@@ -28228,6 +29080,9 @@
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A384" s="8">
+        <v>52</v>
+      </c>
       <c r="B384" s="182" t="s">
         <v>596</v>
       </c>
@@ -28249,6 +29104,9 @@
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A385" s="8">
+        <v>52</v>
+      </c>
       <c r="B385" s="182" t="s">
         <v>596</v>
       </c>
@@ -28270,6 +29128,9 @@
       </c>
     </row>
     <row r="386" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A386" s="8">
+        <v>52</v>
+      </c>
       <c r="B386" s="183" t="s">
         <v>596</v>
       </c>
@@ -28316,6 +29177,9 @@
       </c>
     </row>
     <row r="389" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A389" s="8">
+        <v>53</v>
+      </c>
       <c r="B389" s="182" t="s">
         <v>539</v>
       </c>
@@ -28337,6 +29201,9 @@
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A390" s="8">
+        <v>53</v>
+      </c>
       <c r="B390" s="182" t="s">
         <v>539</v>
       </c>
@@ -28358,6 +29225,9 @@
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A391" s="8">
+        <v>53</v>
+      </c>
       <c r="B391" s="182" t="s">
         <v>539</v>
       </c>
@@ -28379,6 +29249,9 @@
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A392" s="8">
+        <v>53</v>
+      </c>
       <c r="B392" s="182" t="s">
         <v>539</v>
       </c>
@@ -28400,6 +29273,9 @@
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A393" s="8">
+        <v>53</v>
+      </c>
       <c r="B393" s="182" t="s">
         <v>539</v>
       </c>
@@ -28421,6 +29297,9 @@
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A394" s="8">
+        <v>53</v>
+      </c>
       <c r="B394" s="182" t="s">
         <v>539</v>
       </c>
@@ -28442,6 +29321,9 @@
       </c>
     </row>
     <row r="395" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A395" s="8">
+        <v>53</v>
+      </c>
       <c r="B395" s="183" t="s">
         <v>539</v>
       </c>
@@ -28488,6 +29370,9 @@
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A398" s="8">
+        <v>54</v>
+      </c>
       <c r="B398" s="182" t="s">
         <v>540</v>
       </c>
@@ -28509,6 +29394,9 @@
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A399" s="8">
+        <v>54</v>
+      </c>
       <c r="B399" s="182" t="s">
         <v>540</v>
       </c>
@@ -28530,6 +29418,9 @@
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A400" s="8">
+        <v>54</v>
+      </c>
       <c r="B400" s="182" t="s">
         <v>540</v>
       </c>
@@ -28551,6 +29442,9 @@
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A401" s="8">
+        <v>54</v>
+      </c>
       <c r="B401" s="182" t="s">
         <v>540</v>
       </c>
@@ -28572,6 +29466,9 @@
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A402" s="8">
+        <v>54</v>
+      </c>
       <c r="B402" s="182" t="s">
         <v>540</v>
       </c>
@@ -28593,6 +29490,9 @@
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A403" s="8">
+        <v>54</v>
+      </c>
       <c r="B403" s="182" t="s">
         <v>540</v>
       </c>
@@ -28614,6 +29514,9 @@
       </c>
     </row>
     <row r="404" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A404" s="8">
+        <v>54</v>
+      </c>
       <c r="B404" s="183" t="s">
         <v>540</v>
       </c>
@@ -28660,6 +29563,9 @@
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A407" s="8">
+        <v>55</v>
+      </c>
       <c r="B407" s="182" t="s">
         <v>416</v>
       </c>
@@ -28681,6 +29587,9 @@
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A408" s="8">
+        <v>55</v>
+      </c>
       <c r="B408" s="182" t="s">
         <v>416</v>
       </c>
@@ -28702,6 +29611,9 @@
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A409" s="8">
+        <v>55</v>
+      </c>
       <c r="B409" s="182" t="s">
         <v>416</v>
       </c>
@@ -28723,6 +29635,9 @@
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A410" s="8">
+        <v>55</v>
+      </c>
       <c r="B410" s="182" t="s">
         <v>416</v>
       </c>
@@ -28744,6 +29659,9 @@
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A411" s="8">
+        <v>55</v>
+      </c>
       <c r="B411" s="182" t="s">
         <v>416</v>
       </c>
@@ -28765,6 +29683,9 @@
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A412" s="8">
+        <v>55</v>
+      </c>
       <c r="B412" s="182" t="s">
         <v>416</v>
       </c>
@@ -28786,6 +29707,9 @@
       </c>
     </row>
     <row r="413" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A413" s="8">
+        <v>55</v>
+      </c>
       <c r="B413" s="183" t="s">
         <v>416</v>
       </c>
@@ -28861,6 +29785,9 @@
       </c>
     </row>
     <row r="418" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A418" s="8">
+        <v>57</v>
+      </c>
       <c r="B418" s="183" t="s">
         <v>414</v>
       </c>
@@ -28964,6 +29891,9 @@
       </c>
     </row>
     <row r="426" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A426" s="8">
+        <v>1</v>
+      </c>
       <c r="B426" s="183" t="s">
         <v>303</v>
       </c>
@@ -29010,6 +29940,9 @@
       </c>
     </row>
     <row r="429" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A429" s="8">
+        <v>2</v>
+      </c>
       <c r="B429" s="183" t="s">
         <v>304</v>
       </c>
@@ -29056,6 +29989,9 @@
       </c>
     </row>
     <row r="432" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A432" s="146">
+        <v>3</v>
+      </c>
       <c r="B432" s="183" t="s">
         <v>305</v>
       </c>
@@ -29106,6 +30042,9 @@
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A435" s="146">
+        <v>4</v>
+      </c>
       <c r="B435" s="182" t="s">
         <v>306</v>
       </c>
@@ -29127,6 +30066,9 @@
       </c>
     </row>
     <row r="436" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A436" s="146">
+        <v>4</v>
+      </c>
       <c r="B436" s="183" t="s">
         <v>306</v>
       </c>
@@ -29173,6 +30115,9 @@
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A439" s="146">
+        <v>5</v>
+      </c>
       <c r="B439" s="182" t="s">
         <v>682</v>
       </c>
@@ -29194,6 +30139,9 @@
       </c>
     </row>
     <row r="440" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A440" s="146">
+        <v>5</v>
+      </c>
       <c r="B440" s="183" t="s">
         <v>682</v>
       </c>
@@ -29240,6 +30188,9 @@
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A443" s="146">
+        <v>6</v>
+      </c>
       <c r="B443" s="182" t="s">
         <v>683</v>
       </c>
@@ -29261,6 +30212,9 @@
       </c>
     </row>
     <row r="444" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A444" s="146">
+        <v>6</v>
+      </c>
       <c r="B444" s="183" t="s">
         <v>683</v>
       </c>
@@ -29332,6 +30286,9 @@
       </c>
     </row>
     <row r="449" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A449" s="8">
+        <v>8</v>
+      </c>
       <c r="B449" s="183" t="s">
         <v>310</v>
       </c>
@@ -29378,6 +30335,9 @@
       </c>
     </row>
     <row r="452" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A452" s="8">
+        <v>9</v>
+      </c>
       <c r="B452" s="183" t="s">
         <v>379</v>
       </c>
@@ -29424,6 +30384,9 @@
       </c>
     </row>
     <row r="455" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A455" s="8">
+        <v>10</v>
+      </c>
       <c r="B455" s="183" t="s">
         <v>64</v>
       </c>
@@ -29470,6 +30433,9 @@
       </c>
     </row>
     <row r="458" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A458" s="8">
+        <v>11</v>
+      </c>
       <c r="B458" s="183" t="s">
         <v>67</v>
       </c>
@@ -29516,6 +30482,9 @@
       </c>
     </row>
     <row r="461" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A461" s="8">
+        <v>12</v>
+      </c>
       <c r="B461" s="183" t="s">
         <v>69</v>
       </c>
@@ -29562,6 +30531,9 @@
       </c>
     </row>
     <row r="464" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A464" s="8">
+        <v>13</v>
+      </c>
       <c r="B464" s="183" t="s">
         <v>72</v>
       </c>
@@ -29608,6 +30580,9 @@
       </c>
     </row>
     <row r="467" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A467" s="146">
+        <v>14</v>
+      </c>
       <c r="B467" s="183" t="s">
         <v>284</v>
       </c>
@@ -31116,6 +32091,9 @@
       </c>
     </row>
     <row r="588" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A588" s="8">
+        <v>74</v>
+      </c>
       <c r="B588" s="183" t="s">
         <v>324</v>
       </c>
@@ -31162,6 +32140,9 @@
       </c>
     </row>
     <row r="591" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A591" s="8">
+        <v>75</v>
+      </c>
       <c r="B591" s="183" t="s">
         <v>325</v>
       </c>
@@ -31208,6 +32189,9 @@
       </c>
     </row>
     <row r="594" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A594" s="8">
+        <v>76</v>
+      </c>
       <c r="B594" s="183" t="s">
         <v>326</v>
       </c>
@@ -31254,6 +32238,9 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A597" s="8">
+        <v>77</v>
+      </c>
       <c r="B597" s="183" t="s">
         <v>327</v>
       </c>
@@ -31300,6 +32287,9 @@
       </c>
     </row>
     <row r="600" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A600" s="8">
+        <v>78</v>
+      </c>
       <c r="B600" s="183" t="s">
         <v>328</v>
       </c>
@@ -31346,6 +32336,9 @@
       </c>
     </row>
     <row r="603" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A603" s="8">
+        <v>79</v>
+      </c>
       <c r="B603" s="183" t="s">
         <v>329</v>
       </c>
@@ -31392,6 +32385,9 @@
       </c>
     </row>
     <row r="606" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A606" s="8">
+        <v>80</v>
+      </c>
       <c r="B606" s="183" t="s">
         <v>330</v>
       </c>
@@ -31438,6 +32434,9 @@
       </c>
     </row>
     <row r="609" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A609" s="8">
+        <v>81</v>
+      </c>
       <c r="B609" s="183" t="s">
         <v>331</v>
       </c>
@@ -31484,6 +32483,9 @@
       </c>
     </row>
     <row r="612" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A612" s="8">
+        <v>82</v>
+      </c>
       <c r="B612" s="183" t="s">
         <v>332</v>
       </c>
@@ -31530,6 +32532,9 @@
       </c>
     </row>
     <row r="615" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A615" s="8">
+        <v>83</v>
+      </c>
       <c r="B615" s="183" t="s">
         <v>333</v>
       </c>
@@ -31576,6 +32581,9 @@
       </c>
     </row>
     <row r="618" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A618" s="8">
+        <v>84</v>
+      </c>
       <c r="B618" s="183" t="s">
         <v>334</v>
       </c>
@@ -31622,6 +32630,9 @@
       </c>
     </row>
     <row r="621" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A621" s="8">
+        <v>85</v>
+      </c>
       <c r="B621" s="183" t="s">
         <v>335</v>
       </c>
@@ -31668,6 +32679,9 @@
       </c>
     </row>
     <row r="624" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A624" s="8">
+        <v>86</v>
+      </c>
       <c r="B624" s="183" t="s">
         <v>336</v>
       </c>
@@ -31714,6 +32728,9 @@
       </c>
     </row>
     <row r="627" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A627" s="8">
+        <v>87</v>
+      </c>
       <c r="B627" s="183" t="s">
         <v>337</v>
       </c>
@@ -31760,6 +32777,9 @@
       </c>
     </row>
     <row r="630" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A630" s="8">
+        <v>88</v>
+      </c>
       <c r="B630" s="183" t="s">
         <v>338</v>
       </c>
@@ -31806,6 +32826,9 @@
       </c>
     </row>
     <row r="633" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A633" s="8">
+        <v>89</v>
+      </c>
       <c r="B633" s="183" t="s">
         <v>339</v>
       </c>
@@ -31852,6 +32875,9 @@
       </c>
     </row>
     <row r="636" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A636" s="8">
+        <v>90</v>
+      </c>
       <c r="B636" s="183" t="s">
         <v>340</v>
       </c>
@@ -31898,6 +32924,9 @@
       </c>
     </row>
     <row r="639" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A639" s="8">
+        <v>91</v>
+      </c>
       <c r="B639" s="183" t="s">
         <v>341</v>
       </c>
@@ -31944,6 +32973,9 @@
       </c>
     </row>
     <row r="642" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A642" s="8">
+        <v>92</v>
+      </c>
       <c r="B642" s="183" t="s">
         <v>535</v>
       </c>
@@ -31990,6 +33022,9 @@
       </c>
     </row>
     <row r="645" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A645" s="146">
+        <v>93</v>
+      </c>
       <c r="B645" s="183" t="s">
         <v>368</v>
       </c>
@@ -32036,6 +33071,9 @@
       </c>
     </row>
     <row r="648" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A648" s="146">
+        <v>94</v>
+      </c>
       <c r="B648" s="183" t="s">
         <v>409</v>
       </c>
@@ -32082,6 +33120,9 @@
       </c>
     </row>
     <row r="651" spans="1:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A651" s="8">
+        <v>95</v>
+      </c>
       <c r="B651" s="183" t="s">
         <v>408</v>
       </c>
@@ -32128,6 +33169,9 @@
       </c>
     </row>
     <row r="654" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A654" s="8">
+        <v>96</v>
+      </c>
       <c r="B654" s="183" t="s">
         <v>407</v>
       </c>
@@ -32248,6 +33292,9 @@
       </c>
     </row>
     <row r="662" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A662" s="146">
+        <v>100</v>
+      </c>
       <c r="B662" s="182" t="s">
         <v>549</v>
       </c>
@@ -32269,6 +33316,9 @@
       </c>
     </row>
     <row r="663" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A663" s="146">
+        <v>100</v>
+      </c>
       <c r="B663" s="183" t="s">
         <v>549</v>
       </c>
@@ -32315,6 +33365,9 @@
       </c>
     </row>
     <row r="666" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A666" s="146">
+        <v>101</v>
+      </c>
       <c r="B666" s="182" t="s">
         <v>550</v>
       </c>
@@ -32336,6 +33389,9 @@
       </c>
     </row>
     <row r="667" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A667" s="146">
+        <v>101</v>
+      </c>
       <c r="B667" s="183" t="s">
         <v>550</v>
       </c>
@@ -32382,6 +33438,9 @@
       </c>
     </row>
     <row r="670" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A670" s="146">
+        <v>102</v>
+      </c>
       <c r="B670" s="182" t="s">
         <v>551</v>
       </c>
@@ -32403,6 +33462,9 @@
       </c>
     </row>
     <row r="671" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A671" s="146">
+        <v>102</v>
+      </c>
       <c r="B671" s="183" t="s">
         <v>551</v>
       </c>
@@ -32449,6 +33511,9 @@
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A674" s="146">
+        <v>103</v>
+      </c>
       <c r="B674" s="182" t="s">
         <v>552</v>
       </c>
@@ -32470,6 +33535,9 @@
       </c>
     </row>
     <row r="675" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A675" s="146">
+        <v>103</v>
+      </c>
       <c r="B675" s="183" t="s">
         <v>552</v>
       </c>
@@ -32516,6 +33584,9 @@
       </c>
     </row>
     <row r="678" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A678" s="146">
+        <v>104</v>
+      </c>
       <c r="B678" s="182" t="s">
         <v>554</v>
       </c>
@@ -32537,6 +33608,9 @@
       </c>
     </row>
     <row r="679" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A679" s="146">
+        <v>104</v>
+      </c>
       <c r="B679" s="183" t="s">
         <v>554</v>
       </c>
@@ -32583,6 +33657,9 @@
       </c>
     </row>
     <row r="682" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A682" s="146">
+        <v>105</v>
+      </c>
       <c r="B682" s="182" t="s">
         <v>555</v>
       </c>
@@ -32604,6 +33681,9 @@
       </c>
     </row>
     <row r="683" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A683" s="146">
+        <v>105</v>
+      </c>
       <c r="B683" s="183" t="s">
         <v>555</v>
       </c>
@@ -32650,6 +33730,9 @@
       </c>
     </row>
     <row r="686" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A686" s="146">
+        <v>106</v>
+      </c>
       <c r="B686" s="182" t="s">
         <v>556</v>
       </c>
@@ -32671,6 +33754,9 @@
       </c>
     </row>
     <row r="687" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A687" s="146">
+        <v>106</v>
+      </c>
       <c r="B687" s="183" t="s">
         <v>556</v>
       </c>
@@ -32717,6 +33803,9 @@
       </c>
     </row>
     <row r="690" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A690" s="146">
+        <v>107</v>
+      </c>
       <c r="B690" s="182" t="s">
         <v>557</v>
       </c>
@@ -32738,6 +33827,9 @@
       </c>
     </row>
     <row r="691" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A691" s="146">
+        <v>107</v>
+      </c>
       <c r="B691" s="183" t="s">
         <v>557</v>
       </c>
@@ -32784,6 +33876,9 @@
       </c>
     </row>
     <row r="694" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A694" s="146">
+        <v>108</v>
+      </c>
       <c r="B694" s="182" t="s">
         <v>558</v>
       </c>
@@ -32805,6 +33900,9 @@
       </c>
     </row>
     <row r="695" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A695" s="146">
+        <v>108</v>
+      </c>
       <c r="B695" s="183" t="s">
         <v>558</v>
       </c>
@@ -32951,6 +34049,9 @@
       </c>
     </row>
     <row r="706" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A706" s="8">
+        <v>113</v>
+      </c>
       <c r="B706" s="183" t="s">
         <v>566</v>
       </c>
@@ -32997,6 +34098,9 @@
       </c>
     </row>
     <row r="709" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A709" s="8">
+        <v>114</v>
+      </c>
       <c r="B709" s="183" t="s">
         <v>568</v>
       </c>
@@ -33043,6 +34147,9 @@
       </c>
     </row>
     <row r="712" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A712" s="8">
+        <v>115</v>
+      </c>
       <c r="B712" s="183" t="s">
         <v>569</v>
       </c>
@@ -33089,6 +34196,9 @@
       </c>
     </row>
     <row r="715" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A715" s="8">
+        <v>116</v>
+      </c>
       <c r="B715" s="183" t="s">
         <v>571</v>
       </c>
@@ -33135,6 +34245,9 @@
       </c>
     </row>
     <row r="718" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A718" s="8">
+        <v>117</v>
+      </c>
       <c r="B718" s="183" t="s">
         <v>572</v>
       </c>
@@ -33181,6 +34294,9 @@
       </c>
     </row>
     <row r="721" spans="1:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A721" s="8">
+        <v>118</v>
+      </c>
       <c r="B721" s="183" t="s">
         <v>573</v>
       </c>
@@ -33375,6 +34491,9 @@
       </c>
     </row>
     <row r="736" spans="1:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A736" s="8">
+        <v>7</v>
+      </c>
       <c r="B736" s="183" t="s">
         <v>143</v>
       </c>
@@ -33462,6 +34581,9 @@
       </c>
     </row>
     <row r="743" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A743" s="8">
+        <v>10</v>
+      </c>
       <c r="B743" s="182" t="s">
         <v>148</v>
       </c>
@@ -33481,6 +34603,9 @@
       </c>
     </row>
     <row r="744" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A744" s="8">
+        <v>10</v>
+      </c>
       <c r="B744" s="183" t="s">
         <v>148</v>
       </c>
@@ -33569,6 +34694,9 @@
       </c>
     </row>
     <row r="751" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A751" s="8">
+        <v>13</v>
+      </c>
       <c r="B751" s="182" t="s">
         <v>151</v>
       </c>
@@ -33588,6 +34716,9 @@
       </c>
     </row>
     <row r="752" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A752" s="8">
+        <v>13</v>
+      </c>
       <c r="B752" s="183" t="s">
         <v>151</v>
       </c>
@@ -33630,6 +34761,9 @@
       </c>
     </row>
     <row r="755" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A755" s="8">
+        <v>14</v>
+      </c>
       <c r="B755" s="182" t="s">
         <v>152</v>
       </c>
@@ -33649,6 +34783,9 @@
       </c>
     </row>
     <row r="756" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A756" s="8">
+        <v>14</v>
+      </c>
       <c r="B756" s="183" t="s">
         <v>152</v>
       </c>
@@ -33691,6 +34828,9 @@
       </c>
     </row>
     <row r="759" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A759" s="8">
+        <v>15</v>
+      </c>
       <c r="B759" s="182" t="s">
         <v>153</v>
       </c>
@@ -33710,6 +34850,9 @@
       </c>
     </row>
     <row r="760" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A760" s="8">
+        <v>15</v>
+      </c>
       <c r="B760" s="183" t="s">
         <v>153</v>
       </c>
@@ -33752,6 +34895,9 @@
       </c>
     </row>
     <row r="763" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A763" s="8">
+        <v>16</v>
+      </c>
       <c r="B763" s="183" t="s">
         <v>154</v>
       </c>
@@ -33794,6 +34940,9 @@
       </c>
     </row>
     <row r="766" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A766" s="8">
+        <v>17</v>
+      </c>
       <c r="B766" s="182" t="s">
         <v>155</v>
       </c>
@@ -33813,6 +34962,9 @@
       </c>
     </row>
     <row r="767" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A767" s="8">
+        <v>17</v>
+      </c>
       <c r="B767" s="183" t="s">
         <v>155</v>
       </c>
@@ -33855,6 +35007,9 @@
       </c>
     </row>
     <row r="770" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A770" s="8">
+        <v>18</v>
+      </c>
       <c r="B770" s="182" t="s">
         <v>156</v>
       </c>
@@ -33874,6 +35029,9 @@
       </c>
     </row>
     <row r="771" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A771" s="8">
+        <v>18</v>
+      </c>
       <c r="B771" s="183" t="s">
         <v>156</v>
       </c>
@@ -33916,6 +35074,9 @@
       </c>
     </row>
     <row r="774" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A774" s="8">
+        <v>19</v>
+      </c>
       <c r="B774" s="182" t="s">
         <v>157</v>
       </c>
@@ -33935,6 +35096,9 @@
       </c>
     </row>
     <row r="775" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A775" s="8">
+        <v>19</v>
+      </c>
       <c r="B775" s="183" t="s">
         <v>157</v>
       </c>
@@ -33977,6 +35141,9 @@
       </c>
     </row>
     <row r="778" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A778" s="8">
+        <v>20</v>
+      </c>
       <c r="B778" s="183" t="s">
         <v>158</v>
       </c>
@@ -34021,6 +35188,9 @@
       </c>
     </row>
     <row r="781" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A781" s="8">
+        <v>21</v>
+      </c>
       <c r="B781" s="182" t="s">
         <v>159</v>
       </c>
@@ -34042,6 +35212,9 @@
       </c>
     </row>
     <row r="782" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A782" s="8">
+        <v>21</v>
+      </c>
       <c r="B782" s="182" t="s">
         <v>159</v>
       </c>
@@ -34063,6 +35236,9 @@
       </c>
     </row>
     <row r="783" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A783" s="8">
+        <v>21</v>
+      </c>
       <c r="B783" s="183" t="s">
         <v>159</v>
       </c>
@@ -34107,6 +35283,9 @@
       </c>
     </row>
     <row r="786" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A786" s="8">
+        <v>22</v>
+      </c>
       <c r="B786" s="183" t="s">
         <v>462</v>
       </c>
@@ -34149,6 +35328,9 @@
       </c>
     </row>
     <row r="789" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A789" s="8">
+        <v>23</v>
+      </c>
       <c r="B789" s="182" t="s">
         <v>463</v>
       </c>
@@ -34168,6 +35350,9 @@
       </c>
     </row>
     <row r="790" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A790" s="8">
+        <v>23</v>
+      </c>
       <c r="B790" s="183" t="s">
         <v>463</v>
       </c>
@@ -34210,6 +35395,9 @@
       </c>
     </row>
     <row r="793" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A793" s="8">
+        <v>24</v>
+      </c>
       <c r="B793" s="182" t="s">
         <v>465</v>
       </c>
@@ -34229,6 +35417,9 @@
       </c>
     </row>
     <row r="794" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A794" s="8">
+        <v>24</v>
+      </c>
       <c r="B794" s="183" t="s">
         <v>465</v>
       </c>
@@ -34271,6 +35462,9 @@
       </c>
     </row>
     <row r="797" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A797" s="8">
+        <v>25</v>
+      </c>
       <c r="B797" s="182" t="s">
         <v>466</v>
       </c>
@@ -34290,6 +35484,9 @@
       </c>
     </row>
     <row r="798" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A798" s="8">
+        <v>25</v>
+      </c>
       <c r="B798" s="183" t="s">
         <v>466</v>
       </c>
@@ -34332,6 +35529,9 @@
       </c>
     </row>
     <row r="801" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A801" s="8">
+        <v>26</v>
+      </c>
       <c r="B801" s="183" t="s">
         <v>467</v>
       </c>
@@ -34376,6 +35576,9 @@
       </c>
     </row>
     <row r="804" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A804" s="8">
+        <v>27</v>
+      </c>
       <c r="B804" s="183" t="s">
         <v>468</v>
       </c>
@@ -34420,6 +35623,9 @@
       </c>
     </row>
     <row r="807" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A807" s="8">
+        <v>28</v>
+      </c>
       <c r="B807" s="183" t="s">
         <v>469</v>
       </c>
@@ -34462,6 +35668,9 @@
       </c>
     </row>
     <row r="810" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A810" s="8">
+        <v>29</v>
+      </c>
       <c r="B810" s="183" t="s">
         <v>470</v>
       </c>
@@ -34506,6 +35715,9 @@
       </c>
     </row>
     <row r="813" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A813" s="8">
+        <v>30</v>
+      </c>
       <c r="B813" s="183" t="s">
         <v>471</v>
       </c>
@@ -34631,7 +35843,7 @@
         <v>625</v>
       </c>
       <c r="C823" s="221" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D823" s="167"/>
       <c r="E823" s="28">
@@ -34654,7 +35866,7 @@
         <v>626</v>
       </c>
       <c r="C825" s="221" t="s">
-        <v>163</v>
+        <v>763</v>
       </c>
       <c r="D825" s="167"/>
       <c r="E825" s="28">
@@ -34677,7 +35889,7 @@
         <v>627</v>
       </c>
       <c r="C827" s="221" t="s">
-        <v>165</v>
+        <v>764</v>
       </c>
       <c r="D827" s="167"/>
       <c r="E827" s="28">
@@ -34700,7 +35912,7 @@
         <v>628</v>
       </c>
       <c r="C829" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D829" s="167"/>
       <c r="E829" s="28">
@@ -34723,7 +35935,7 @@
         <v>629</v>
       </c>
       <c r="C831" s="221" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D831" s="167"/>
       <c r="E831" s="28">
@@ -34746,7 +35958,7 @@
         <v>630</v>
       </c>
       <c r="C833" s="221" t="s">
-        <v>167</v>
+        <v>765</v>
       </c>
       <c r="D833" s="167"/>
       <c r="E833" s="28">
@@ -34769,7 +35981,7 @@
         <v>631</v>
       </c>
       <c r="C835" s="221" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D835" s="167"/>
       <c r="E835" s="28">
@@ -34792,7 +36004,7 @@
         <v>632</v>
       </c>
       <c r="C837" s="221" t="s">
-        <v>163</v>
+        <v>763</v>
       </c>
       <c r="D837" s="167"/>
       <c r="E837" s="28">
@@ -34815,7 +36027,7 @@
         <v>633</v>
       </c>
       <c r="C839" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D839" s="167"/>
       <c r="E839" s="28">
@@ -34838,7 +36050,7 @@
         <v>634</v>
       </c>
       <c r="C841" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D841" s="167"/>
       <c r="E841" s="28">
@@ -34861,7 +36073,7 @@
         <v>635</v>
       </c>
       <c r="C843" s="221" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D843" s="167"/>
       <c r="E843" s="28">
@@ -34884,7 +36096,7 @@
         <v>636</v>
       </c>
       <c r="C845" s="221" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D845" s="167"/>
       <c r="E845" s="28">
@@ -34907,7 +36119,7 @@
         <v>637</v>
       </c>
       <c r="C847" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D847" s="167"/>
       <c r="E847" s="28">
@@ -34930,7 +36142,7 @@
         <v>638</v>
       </c>
       <c r="C849" s="221" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D849" s="167"/>
       <c r="E849" s="28">
@@ -34953,7 +36165,7 @@
         <v>639</v>
       </c>
       <c r="C851" s="221" t="s">
-        <v>171</v>
+        <v>762</v>
       </c>
       <c r="D851" s="167"/>
       <c r="E851" s="28">
@@ -34976,7 +36188,7 @@
         <v>640</v>
       </c>
       <c r="C853" s="221" t="s">
-        <v>163</v>
+        <v>763</v>
       </c>
       <c r="D853" s="167"/>
       <c r="E853" s="28">
@@ -34999,7 +36211,7 @@
         <v>641</v>
       </c>
       <c r="C855" s="222" t="s">
-        <v>173</v>
+        <v>762</v>
       </c>
       <c r="D855" s="171"/>
       <c r="E855" s="147">
@@ -35024,7 +36236,7 @@
         <v>642</v>
       </c>
       <c r="C857" s="222" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D857" s="171" t="s">
         <v>219</v>
@@ -35051,7 +36263,7 @@
         <v>643</v>
       </c>
       <c r="C859" s="222" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D859" s="171" t="s">
         <v>219</v>
@@ -35078,7 +36290,7 @@
         <v>613</v>
       </c>
       <c r="C861" s="222" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D861" s="171"/>
       <c r="E861" s="147"/>
@@ -35101,7 +36313,7 @@
         <v>644</v>
       </c>
       <c r="C863" s="222" t="s">
-        <v>176</v>
+        <v>762</v>
       </c>
       <c r="D863" s="171"/>
       <c r="E863" s="147">
@@ -35124,7 +36336,7 @@
         <v>645</v>
       </c>
       <c r="C865" s="222" t="s">
-        <v>177</v>
+        <v>766</v>
       </c>
       <c r="D865" s="171"/>
       <c r="E865" s="147">
@@ -35147,7 +36359,7 @@
         <v>646</v>
       </c>
       <c r="C867" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D867" s="167"/>
       <c r="E867" s="28">
@@ -35170,7 +36382,7 @@
         <v>647</v>
       </c>
       <c r="C869" s="221" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D869" s="167"/>
       <c r="E869" s="28">
@@ -35193,7 +36405,7 @@
         <v>648</v>
       </c>
       <c r="C871" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D871" s="167"/>
       <c r="E871" s="28">
@@ -35216,7 +36428,7 @@
         <v>649</v>
       </c>
       <c r="C873" s="221" t="s">
-        <v>171</v>
+        <v>762</v>
       </c>
       <c r="D873" s="167"/>
       <c r="E873" s="28">
@@ -35239,7 +36451,7 @@
         <v>650</v>
       </c>
       <c r="C875" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D875" s="167"/>
       <c r="E875" s="28">
@@ -35262,7 +36474,7 @@
         <v>651</v>
       </c>
       <c r="C877" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D877" s="167"/>
       <c r="E877" s="28">
@@ -35285,7 +36497,7 @@
         <v>652</v>
       </c>
       <c r="C879" s="221" t="s">
-        <v>171</v>
+        <v>762</v>
       </c>
       <c r="D879" s="167"/>
       <c r="E879" s="28">
@@ -35308,7 +36520,7 @@
         <v>653</v>
       </c>
       <c r="C881" s="221" t="s">
-        <v>171</v>
+        <v>762</v>
       </c>
       <c r="D881" s="167"/>
       <c r="E881" s="28">
@@ -35331,7 +36543,7 @@
         <v>654</v>
       </c>
       <c r="C883" s="221" t="s">
-        <v>171</v>
+        <v>762</v>
       </c>
       <c r="D883" s="167"/>
       <c r="E883" s="28">
@@ -35354,7 +36566,7 @@
         <v>655</v>
       </c>
       <c r="C885" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D885" s="167" t="s">
         <v>483</v>
@@ -35379,7 +36591,7 @@
         <v>501</v>
       </c>
       <c r="C887" s="221" t="s">
-        <v>171</v>
+        <v>762</v>
       </c>
       <c r="D887" s="167"/>
       <c r="E887" s="28">
@@ -35402,7 +36614,7 @@
         <v>502</v>
       </c>
       <c r="C889" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D889" s="167"/>
       <c r="E889" s="28">
@@ -35448,7 +36660,7 @@
         <v>603</v>
       </c>
       <c r="C893" s="216" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D893" s="156"/>
       <c r="E893" s="13">
@@ -35463,11 +36675,14 @@
       </c>
     </row>
     <row r="894" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A894" s="8">
+        <v>37</v>
+      </c>
       <c r="B894" s="182" t="s">
         <v>604</v>
       </c>
       <c r="C894" s="224" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D894" s="157"/>
       <c r="E894" s="6">
@@ -35482,11 +36697,14 @@
       </c>
     </row>
     <row r="895" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A895" s="8">
+        <v>37</v>
+      </c>
       <c r="B895" s="183" t="s">
         <v>605</v>
       </c>
       <c r="C895" s="223" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D895" s="158"/>
       <c r="E895" s="17">
@@ -35509,7 +36727,7 @@
         <v>689</v>
       </c>
       <c r="C897" s="216" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D897" s="156"/>
       <c r="E897" s="13">
@@ -35524,11 +36742,14 @@
       </c>
     </row>
     <row r="898" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A898" s="8">
+        <v>38</v>
+      </c>
       <c r="B898" s="182" t="s">
         <v>690</v>
       </c>
       <c r="C898" s="224" t="s">
-        <v>163</v>
+        <v>763</v>
       </c>
       <c r="D898" s="157"/>
       <c r="E898" s="6">
@@ -35543,11 +36764,14 @@
       </c>
     </row>
     <row r="899" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A899" s="8">
+        <v>38</v>
+      </c>
       <c r="B899" s="182" t="s">
         <v>602</v>
       </c>
       <c r="C899" s="224" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D899" s="157"/>
       <c r="E899" s="6">
@@ -35562,11 +36786,14 @@
       </c>
     </row>
     <row r="900" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A900" s="8">
+        <v>38</v>
+      </c>
       <c r="B900" s="182" t="s">
         <v>691</v>
       </c>
       <c r="C900" s="224" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D900" s="157"/>
       <c r="E900" s="6">
@@ -35581,11 +36808,14 @@
       </c>
     </row>
     <row r="901" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A901" s="8">
+        <v>38</v>
+      </c>
       <c r="B901" s="183" t="s">
         <v>692</v>
       </c>
       <c r="C901" s="223" t="s">
-        <v>162</v>
+        <v>762</v>
       </c>
       <c r="D901" s="158"/>
       <c r="E901" s="17">
@@ -35629,7 +36859,7 @@
         <v>656</v>
       </c>
       <c r="C905" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D905" s="167" t="s">
         <v>183</v>
@@ -35654,7 +36884,7 @@
         <v>657</v>
       </c>
       <c r="C907" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D907" s="167" t="s">
         <v>184</v>
@@ -35679,7 +36909,7 @@
         <v>658</v>
       </c>
       <c r="C909" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D909" s="167" t="s">
         <v>185</v>
@@ -35704,7 +36934,7 @@
         <v>622</v>
       </c>
       <c r="C911" s="221" t="s">
-        <v>166</v>
+        <v>765</v>
       </c>
       <c r="D911" s="167" t="s">
         <v>186</v>
@@ -36470,6 +37700,9 @@
       </c>
     </row>
     <row r="978" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A978" s="8">
+        <v>4</v>
+      </c>
       <c r="B978" s="183" t="s">
         <v>218</v>
       </c>
@@ -36815,6 +38048,9 @@
       </c>
     </row>
     <row r="1007" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1007" s="8">
+        <v>18</v>
+      </c>
       <c r="B1007" s="183" t="s">
         <v>233</v>
       </c>
@@ -36903,6 +38139,9 @@
       </c>
     </row>
     <row r="1014" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1014" s="8">
+        <v>21</v>
+      </c>
       <c r="B1014" s="182" t="s">
         <v>238</v>
       </c>
@@ -36921,6 +38160,9 @@
       </c>
     </row>
     <row r="1015" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1015" s="8">
+        <v>21</v>
+      </c>
       <c r="B1015" s="182" t="s">
         <v>238</v>
       </c>
@@ -36939,6 +38181,9 @@
       </c>
     </row>
     <row r="1016" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1016" s="8">
+        <v>21</v>
+      </c>
       <c r="B1016" s="182" t="s">
         <v>238</v>
       </c>
@@ -36957,6 +38202,9 @@
       </c>
     </row>
     <row r="1017" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1017" s="8">
+        <v>21</v>
+      </c>
       <c r="B1017" s="182" t="s">
         <v>238</v>
       </c>
@@ -36975,6 +38223,9 @@
       </c>
     </row>
     <row r="1018" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1018" s="8">
+        <v>21</v>
+      </c>
       <c r="B1018" s="182" t="s">
         <v>238</v>
       </c>
@@ -36993,6 +38244,9 @@
       </c>
     </row>
     <row r="1019" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1019" s="8">
+        <v>21</v>
+      </c>
       <c r="B1019" s="182" t="s">
         <v>238</v>
       </c>
@@ -37011,6 +38265,9 @@
       </c>
     </row>
     <row r="1020" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1020" s="8">
+        <v>21</v>
+      </c>
       <c r="B1020" s="182" t="s">
         <v>238</v>
       </c>
@@ -37029,6 +38286,9 @@
       </c>
     </row>
     <row r="1021" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1021" s="8">
+        <v>21</v>
+      </c>
       <c r="B1021" s="183" t="s">
         <v>238</v>
       </c>
@@ -37071,6 +38331,9 @@
       </c>
     </row>
     <row r="1024" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1024" s="8">
+        <v>22</v>
+      </c>
       <c r="B1024" s="182" t="s">
         <v>241</v>
       </c>
@@ -37089,6 +38352,9 @@
       </c>
     </row>
     <row r="1025" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1025" s="8">
+        <v>22</v>
+      </c>
       <c r="B1025" s="183" t="s">
         <v>241</v>
       </c>
@@ -37133,6 +38399,9 @@
       </c>
     </row>
     <row r="1028" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1028" s="8">
+        <v>23</v>
+      </c>
       <c r="B1028" s="183" t="s">
         <v>715</v>
       </c>
@@ -37252,6 +38521,9 @@
       </c>
     </row>
     <row r="1037" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1037" s="8">
+        <v>27</v>
+      </c>
       <c r="B1037" s="183" t="s">
         <v>717</v>
       </c>
@@ -37298,6 +38570,9 @@
       </c>
     </row>
     <row r="1040" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1040" s="8">
+        <v>28</v>
+      </c>
       <c r="B1040" s="182" t="s">
         <v>718</v>
       </c>
@@ -37319,6 +38594,9 @@
       </c>
     </row>
     <row r="1041" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1041" s="8">
+        <v>28</v>
+      </c>
       <c r="B1041" s="182" t="s">
         <v>718</v>
       </c>
@@ -37340,6 +38618,9 @@
       </c>
     </row>
     <row r="1042" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1042" s="8">
+        <v>28</v>
+      </c>
       <c r="B1042" s="183" t="s">
         <v>718</v>
       </c>
@@ -37386,6 +38667,9 @@
       </c>
     </row>
     <row r="1045" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1045" s="8">
+        <v>29</v>
+      </c>
       <c r="B1045" s="182" t="s">
         <v>713</v>
       </c>
@@ -37407,6 +38691,9 @@
       </c>
     </row>
     <row r="1046" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1046" s="8">
+        <v>29</v>
+      </c>
       <c r="B1046" s="183" t="s">
         <v>713</v>
       </c>
@@ -37453,6 +38740,9 @@
       </c>
     </row>
     <row r="1049" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1049" s="8">
+        <v>30</v>
+      </c>
       <c r="B1049" s="183" t="s">
         <v>719</v>
       </c>
@@ -37574,6 +38864,9 @@
       </c>
     </row>
     <row r="1058" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1058" s="146">
+        <v>34</v>
+      </c>
       <c r="B1058" s="183" t="s">
         <v>723</v>
       </c>
@@ -37643,6 +38936,9 @@
       </c>
     </row>
     <row r="1063" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1063" s="8">
+        <v>36</v>
+      </c>
       <c r="B1063" s="182" t="s">
         <v>402</v>
       </c>
@@ -37661,6 +38957,9 @@
       </c>
     </row>
     <row r="1064" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1064" s="8">
+        <v>36</v>
+      </c>
       <c r="B1064" s="183" t="s">
         <v>402</v>
       </c>
@@ -37703,6 +39002,9 @@
       </c>
     </row>
     <row r="1067" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1067" s="8">
+        <v>37</v>
+      </c>
       <c r="B1067" s="182" t="s">
         <v>403</v>
       </c>
@@ -37721,6 +39023,9 @@
       </c>
     </row>
     <row r="1068" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1068" s="8">
+        <v>37</v>
+      </c>
       <c r="B1068" s="183" t="s">
         <v>403</v>
       </c>
@@ -37763,6 +39068,9 @@
       </c>
     </row>
     <row r="1071" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1071" s="8">
+        <v>38</v>
+      </c>
       <c r="B1071" s="183" t="s">
         <v>404</v>
       </c>
@@ -37807,6 +39115,9 @@
       </c>
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1074" s="8">
+        <v>39</v>
+      </c>
       <c r="B1074" s="182" t="s">
         <v>726</v>
       </c>
@@ -37828,6 +39139,9 @@
       </c>
     </row>
     <row r="1075" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1075" s="8">
+        <v>39</v>
+      </c>
       <c r="B1075" s="183" t="s">
         <v>726</v>
       </c>
@@ -37874,6 +39188,9 @@
       </c>
     </row>
     <row r="1078" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1078" s="8">
+        <v>40</v>
+      </c>
       <c r="B1078" s="183" t="s">
         <v>727</v>
       </c>
@@ -37920,6 +39237,9 @@
       </c>
     </row>
     <row r="1081" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1081" s="8">
+        <v>41</v>
+      </c>
       <c r="B1081" s="183" t="s">
         <v>728</v>
       </c>
@@ -37966,6 +39286,9 @@
       </c>
     </row>
     <row r="1084" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1084" s="8">
+        <v>42</v>
+      </c>
       <c r="B1084" s="183" t="s">
         <v>729</v>
       </c>
@@ -38162,6 +39485,9 @@
       </c>
     </row>
     <row r="1099" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1099" s="8">
+        <v>49</v>
+      </c>
       <c r="B1099" s="183" t="s">
         <v>737</v>
       </c>
@@ -38208,6 +39534,9 @@
       </c>
     </row>
     <row r="1102" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1102" s="8">
+        <v>50</v>
+      </c>
       <c r="B1102" s="182" t="s">
         <v>276</v>
       </c>
@@ -38229,6 +39558,9 @@
       </c>
     </row>
     <row r="1103" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1103" s="8">
+        <v>50</v>
+      </c>
       <c r="B1103" s="183" t="s">
         <v>276</v>
       </c>
@@ -38275,6 +39607,9 @@
       </c>
     </row>
     <row r="1106" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1106" s="8">
+        <v>51</v>
+      </c>
       <c r="B1106" s="182" t="s">
         <v>448</v>
       </c>
@@ -38296,6 +39631,9 @@
       </c>
     </row>
     <row r="1107" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1107" s="8">
+        <v>51</v>
+      </c>
       <c r="B1107" s="183" t="s">
         <v>448</v>
       </c>
@@ -38392,6 +39730,9 @@
       </c>
     </row>
     <row r="1114" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1114" s="8">
+        <v>54</v>
+      </c>
       <c r="B1114" s="182" t="s">
         <v>280</v>
       </c>
@@ -38413,6 +39754,9 @@
       </c>
     </row>
     <row r="1115" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1115" s="8">
+        <v>54</v>
+      </c>
       <c r="B1115" s="182" t="s">
         <v>280</v>
       </c>
@@ -38434,6 +39778,9 @@
       </c>
     </row>
     <row r="1116" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1116" s="8">
+        <v>54</v>
+      </c>
       <c r="B1116" s="182" t="s">
         <v>280</v>
       </c>
@@ -38455,6 +39802,9 @@
       </c>
     </row>
     <row r="1117" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1117" s="8">
+        <v>54</v>
+      </c>
       <c r="B1117" s="183" t="s">
         <v>280</v>
       </c>
@@ -38501,6 +39851,9 @@
       </c>
     </row>
     <row r="1120" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1120" s="8">
+        <v>55</v>
+      </c>
       <c r="B1120" s="183" t="s">
         <v>405</v>
       </c>
@@ -38547,6 +39900,9 @@
       </c>
     </row>
     <row r="1123" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1123" s="8">
+        <v>56</v>
+      </c>
       <c r="B1123" s="183" t="s">
         <v>406</v>
       </c>
@@ -38593,6 +39949,9 @@
       </c>
     </row>
     <row r="1126" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1126" s="8">
+        <v>57</v>
+      </c>
       <c r="B1126" s="183" t="s">
         <v>281</v>
       </c>
@@ -38639,6 +39998,9 @@
       </c>
     </row>
     <row r="1129" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1129" s="8">
+        <v>58</v>
+      </c>
       <c r="B1129" s="182" t="s">
         <v>282</v>
       </c>
@@ -38660,6 +40022,9 @@
       </c>
     </row>
     <row r="1130" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1130" s="8">
+        <v>58</v>
+      </c>
       <c r="B1130" s="183" t="s">
         <v>282</v>
       </c>
@@ -38704,6 +40069,9 @@
       </c>
     </row>
     <row r="1133" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1133" s="8">
+        <v>1</v>
+      </c>
       <c r="B1133" s="183" t="s">
         <v>275</v>
       </c>
@@ -38746,6 +40114,9 @@
       </c>
     </row>
     <row r="1136" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1136" s="8">
+        <v>2</v>
+      </c>
       <c r="B1136" s="182" t="s">
         <v>457</v>
       </c>
@@ -38764,6 +40135,9 @@
       </c>
     </row>
     <row r="1137" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1137" s="8">
+        <v>2</v>
+      </c>
       <c r="B1137" s="182" t="s">
         <v>457</v>
       </c>
@@ -38782,6 +40156,9 @@
       </c>
     </row>
     <row r="1138" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1138" s="8">
+        <v>2</v>
+      </c>
       <c r="B1138" s="183" t="s">
         <v>457</v>
       </c>
@@ -38829,6 +40206,9 @@
       </c>
     </row>
     <row r="1142" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1142" s="8">
+        <v>3</v>
+      </c>
       <c r="B1142" s="183" t="s">
         <v>661</v>
       </c>
@@ -38871,6 +40251,9 @@
       </c>
     </row>
     <row r="1145" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1145" s="8">
+        <v>4</v>
+      </c>
       <c r="B1145" s="183" t="s">
         <v>662</v>
       </c>
@@ -39005,6 +40388,9 @@
       </c>
     </row>
     <row r="1156" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1156" s="8">
+        <v>9</v>
+      </c>
       <c r="B1156" s="182" t="s">
         <v>668</v>
       </c>
@@ -39024,6 +40410,9 @@
       </c>
     </row>
     <row r="1157" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1157" s="8">
+        <v>9</v>
+      </c>
       <c r="B1157" s="182" t="s">
         <v>668</v>
       </c>
@@ -39043,6 +40432,9 @@
       </c>
     </row>
     <row r="1158" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1158" s="8">
+        <v>9</v>
+      </c>
       <c r="B1158" s="183" t="s">
         <v>670</v>
       </c>
@@ -39085,6 +40477,9 @@
       </c>
     </row>
     <row r="1161" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1161" s="8">
+        <v>10</v>
+      </c>
       <c r="B1161" s="182" t="s">
         <v>671</v>
       </c>
@@ -39104,6 +40499,9 @@
       </c>
     </row>
     <row r="1162" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1162" s="8">
+        <v>10</v>
+      </c>
       <c r="B1162" s="183" t="s">
         <v>671</v>
       </c>
@@ -39148,6 +40546,9 @@
       </c>
     </row>
     <row r="1165" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1165" s="8">
+        <v>11</v>
+      </c>
       <c r="B1165" s="182" t="s">
         <v>673</v>
       </c>
@@ -39167,6 +40568,9 @@
       </c>
     </row>
     <row r="1166" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1166" s="8">
+        <v>11</v>
+      </c>
       <c r="B1166" s="183" t="s">
         <v>673</v>
       </c>
@@ -39186,6 +40590,9 @@
       </c>
     </row>
     <row r="1167" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1167" s="8">
+        <v>12</v>
+      </c>
       <c r="B1167" s="182" t="s">
         <v>674</v>
       </c>
@@ -39203,6 +40610,9 @@
       </c>
     </row>
     <row r="1168" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1168" s="8">
+        <v>13</v>
+      </c>
       <c r="B1168" s="182" t="s">
         <v>675</v>
       </c>
@@ -39222,6 +40632,9 @@
       </c>
     </row>
     <row r="1169" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1169" s="8">
+        <v>14</v>
+      </c>
       <c r="B1169" s="182" t="s">
         <v>676</v>
       </c>
@@ -39239,6 +40652,9 @@
       </c>
     </row>
     <row r="1170" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1170" s="8">
+        <v>15</v>
+      </c>
       <c r="B1170" s="182" t="s">
         <v>677</v>
       </c>
@@ -39256,6 +40672,9 @@
       </c>
     </row>
     <row r="1171" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1171" s="8">
+        <v>15</v>
+      </c>
       <c r="B1171" s="183" t="s">
         <v>678</v>
       </c>
@@ -39275,7 +40694,7 @@
     <row r="1172" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="1173" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1173" s="8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B1173" s="181" t="s">
         <v>672</v>
@@ -39296,6 +40715,9 @@
       </c>
     </row>
     <row r="1174" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1174" s="8">
+        <v>16</v>
+      </c>
       <c r="B1174" s="182" t="s">
         <v>672</v>
       </c>
@@ -39315,6 +40737,9 @@
       </c>
     </row>
     <row r="1175" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1175" s="8">
+        <v>16</v>
+      </c>
       <c r="B1175" s="182" t="s">
         <v>672</v>
       </c>
@@ -39334,6 +40759,9 @@
       </c>
     </row>
     <row r="1176" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1176" s="8">
+        <v>16</v>
+      </c>
       <c r="B1176" s="182" t="s">
         <v>672</v>
       </c>
@@ -39353,6 +40781,9 @@
       </c>
     </row>
     <row r="1177" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1177" s="8">
+        <v>16</v>
+      </c>
       <c r="B1177" s="182" t="s">
         <v>672</v>
       </c>
@@ -39372,6 +40803,9 @@
       </c>
     </row>
     <row r="1178" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1178" s="8">
+        <v>16</v>
+      </c>
       <c r="B1178" s="183" t="s">
         <v>672</v>
       </c>
@@ -39393,7 +40827,7 @@
     <row r="1179" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="1180" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1180" s="8">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B1180" s="181" t="s">
         <v>679</v>
@@ -39414,6 +40848,9 @@
       </c>
     </row>
     <row r="1181" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1181" s="8">
+        <v>17</v>
+      </c>
       <c r="B1181" s="182" t="s">
         <v>679</v>
       </c>
@@ -39433,6 +40870,9 @@
       </c>
     </row>
     <row r="1182" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1182" s="8">
+        <v>17</v>
+      </c>
       <c r="B1182" s="182" t="s">
         <v>679</v>
       </c>
@@ -39452,6 +40892,9 @@
       </c>
     </row>
     <row r="1183" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1183" s="8">
+        <v>17</v>
+      </c>
       <c r="B1183" s="182" t="s">
         <v>679</v>
       </c>
@@ -39471,6 +40914,9 @@
       </c>
     </row>
     <row r="1184" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1184" s="8">
+        <v>17</v>
+      </c>
       <c r="B1184" s="182" t="s">
         <v>679</v>
       </c>
@@ -39490,6 +40936,9 @@
       </c>
     </row>
     <row r="1185" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1185" s="8">
+        <v>17</v>
+      </c>
       <c r="B1185" s="183" t="s">
         <v>679</v>
       </c>
@@ -39511,7 +40960,7 @@
     <row r="1186" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="1187" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1187" s="8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B1187" s="181" t="s">
         <v>681</v>
@@ -39532,6 +40981,9 @@
       </c>
     </row>
     <row r="1188" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1188" s="8">
+        <v>18</v>
+      </c>
       <c r="B1188" s="182" t="s">
         <v>681</v>
       </c>
@@ -39551,6 +41003,9 @@
       </c>
     </row>
     <row r="1189" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1189" s="8">
+        <v>18</v>
+      </c>
       <c r="B1189" s="183" t="s">
         <v>681</v>
       </c>
